--- a/dateTermistori.xlsx
+++ b/dateTermistori.xlsx
@@ -1,25 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29912"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WIP\EVR\EVR_terminal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{EA855654-3A41-450E-BD70-2B1E68C997CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0AEC31C7-8AD3-4C4E-A8B7-0C05811DCF69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="7740" windowWidth="14610" windowHeight="7845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foaie1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -47,7 +57,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -359,7 +369,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E82"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
@@ -367,7 +377,7 @@
     <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -384,7 +394,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>30</v>
       </c>
@@ -398,7 +408,7 @@
         <v>2708</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>31</v>
       </c>
@@ -412,7 +422,7 @@
         <v>2670</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>32</v>
       </c>
@@ -426,7 +436,7 @@
         <v>2640</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>33</v>
       </c>
@@ -440,7 +450,7 @@
         <v>2605</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>34</v>
       </c>
@@ -454,7 +464,7 @@
         <v>2575</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>35</v>
       </c>
@@ -468,7 +478,7 @@
         <v>2540</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>36</v>
       </c>
@@ -482,7 +492,7 @@
         <v>2505</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>37</v>
       </c>
@@ -496,7 +506,7 @@
         <v>2475</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>38</v>
       </c>
@@ -510,7 +520,7 @@
         <v>2440</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>39</v>
       </c>
@@ -524,7 +534,7 @@
         <v>2405</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>40</v>
       </c>
@@ -538,7 +548,7 @@
         <v>2375</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>41</v>
       </c>
@@ -552,7 +562,7 @@
         <v>2350</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>42</v>
       </c>
@@ -566,7 +576,7 @@
         <v>2315</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>43</v>
       </c>
@@ -580,7 +590,7 @@
         <v>2280</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>44</v>
       </c>
@@ -594,7 +604,7 @@
         <v>2235</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4">
       <c r="A17">
         <v>45</v>
       </c>
@@ -608,7 +618,7 @@
         <v>2205</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4">
       <c r="A18">
         <v>46</v>
       </c>
@@ -622,7 +632,7 @@
         <v>2170</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4">
       <c r="A19">
         <v>47</v>
       </c>
@@ -636,7 +646,7 @@
         <v>2140</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4">
       <c r="A20">
         <v>48</v>
       </c>
@@ -650,7 +660,7 @@
         <v>2115</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4">
       <c r="A21">
         <v>49</v>
       </c>
@@ -664,7 +674,7 @@
         <v>2085</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4">
       <c r="A22">
         <v>50</v>
       </c>
@@ -678,7 +688,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4">
       <c r="A23">
         <v>51</v>
       </c>
@@ -692,7 +702,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4">
       <c r="A24">
         <v>52</v>
       </c>
@@ -706,7 +716,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4">
       <c r="A25">
         <v>53</v>
       </c>
@@ -720,7 +730,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4">
       <c r="A26">
         <v>54</v>
       </c>
@@ -734,7 +744,7 @@
         <v>1930</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4">
       <c r="A27">
         <v>55</v>
       </c>
@@ -748,7 +758,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4">
       <c r="A28">
         <v>56</v>
       </c>
@@ -762,7 +772,7 @@
         <v>1875</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4">
       <c r="A29">
         <v>57</v>
       </c>
@@ -776,7 +786,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4">
       <c r="A30">
         <v>58</v>
       </c>
@@ -790,7 +800,7 @@
         <v>1815</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4">
       <c r="A31">
         <v>59</v>
       </c>
@@ -804,7 +814,7 @@
         <v>1790</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4">
       <c r="A32">
         <v>60</v>
       </c>
@@ -818,7 +828,7 @@
         <v>1760</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4">
       <c r="A33">
         <v>61</v>
       </c>
@@ -832,7 +842,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4">
       <c r="A34">
         <v>62</v>
       </c>
@@ -846,7 +856,7 @@
         <v>1705</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4">
       <c r="A35">
         <v>63</v>
       </c>
@@ -860,7 +870,7 @@
         <v>1680</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4">
       <c r="A36">
         <v>64</v>
       </c>
@@ -874,7 +884,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4">
       <c r="A37">
         <v>65</v>
       </c>
@@ -888,7 +898,7 @@
         <v>1630</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4">
       <c r="A38">
         <v>66</v>
       </c>
@@ -902,7 +912,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4">
       <c r="A39">
         <v>67</v>
       </c>
@@ -916,7 +926,7 @@
         <v>1580</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4">
       <c r="A40">
         <v>68</v>
       </c>
@@ -930,7 +940,7 @@
         <v>1558</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4">
       <c r="A41">
         <v>69</v>
       </c>
@@ -944,209 +954,578 @@
         <v>1533</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4">
       <c r="A42">
         <v>70</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B42">
+        <v>70.400000000000006</v>
+      </c>
+      <c r="C42">
+        <v>66</v>
+      </c>
+      <c r="D42">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
       <c r="A43">
         <v>71</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B43">
+        <v>70.900000000000006</v>
+      </c>
+      <c r="C43">
+        <v>68</v>
+      </c>
+      <c r="D43">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
       <c r="A44">
         <v>72</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B44">
+        <v>71.8</v>
+      </c>
+      <c r="C44">
+        <v>68</v>
+      </c>
+      <c r="D44">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
       <c r="A45">
         <v>73</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B45">
+        <v>72.8</v>
+      </c>
+      <c r="C45">
+        <v>69</v>
+      </c>
+      <c r="D45">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
       <c r="A46">
         <v>74</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B46">
+        <v>73.900000000000006</v>
+      </c>
+      <c r="C46">
+        <v>70</v>
+      </c>
+      <c r="D46">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
       <c r="A47">
         <v>75</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B47">
+        <v>74.599999999999994</v>
+      </c>
+      <c r="C47">
+        <v>72</v>
+      </c>
+      <c r="D47">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
       <c r="A48">
         <v>76</v>
       </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B48">
+        <v>75.900000000000006</v>
+      </c>
+      <c r="C48">
+        <v>74</v>
+      </c>
+      <c r="D48">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
       <c r="A49">
         <v>77</v>
       </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B49">
+        <v>76.7</v>
+      </c>
+      <c r="C49">
+        <v>75</v>
+      </c>
+      <c r="D49">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
       <c r="A50">
         <v>78</v>
       </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B50">
+        <v>77.900000000000006</v>
+      </c>
+      <c r="C50">
+        <v>77</v>
+      </c>
+      <c r="D50">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
       <c r="A51">
         <v>79</v>
       </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B51">
+        <v>79.2</v>
+      </c>
+      <c r="C51">
+        <v>72</v>
+      </c>
+      <c r="D51">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
       <c r="A52">
         <v>80</v>
       </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B52">
+        <v>79.900000000000006</v>
+      </c>
+      <c r="C52">
+        <v>74</v>
+      </c>
+      <c r="D52">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
       <c r="A53">
         <v>81</v>
       </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B53">
+        <v>80.8</v>
+      </c>
+      <c r="C53">
+        <v>76</v>
+      </c>
+      <c r="D53">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
       <c r="A54">
         <v>82</v>
       </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B54">
+        <v>82.1</v>
+      </c>
+      <c r="C54">
+        <v>78</v>
+      </c>
+      <c r="D54">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
       <c r="A55">
         <v>83</v>
       </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B55">
+        <v>82.8</v>
+      </c>
+      <c r="C55">
+        <v>79</v>
+      </c>
+      <c r="D55">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
       <c r="A56">
         <v>84</v>
       </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B56">
+        <v>83.9</v>
+      </c>
+      <c r="C56">
+        <v>79</v>
+      </c>
+      <c r="D56">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
       <c r="A57">
         <v>85</v>
       </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B57">
+        <v>84.7</v>
+      </c>
+      <c r="C57">
+        <v>80</v>
+      </c>
+      <c r="D57">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
       <c r="A58">
         <v>86</v>
       </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B58">
+        <v>85.9</v>
+      </c>
+      <c r="C58">
+        <v>81</v>
+      </c>
+      <c r="D58">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
       <c r="A59">
         <v>87</v>
       </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B59">
+        <v>86.8</v>
+      </c>
+      <c r="C59">
+        <v>82</v>
+      </c>
+      <c r="D59">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
       <c r="A60">
         <v>88</v>
       </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B60">
+        <v>87.8</v>
+      </c>
+      <c r="C60">
+        <v>84</v>
+      </c>
+      <c r="D60">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
       <c r="A61">
         <v>89</v>
       </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B61">
+        <v>88.9</v>
+      </c>
+      <c r="C61">
+        <v>85</v>
+      </c>
+      <c r="D61">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
       <c r="A62">
         <v>90</v>
       </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B62">
+        <v>89.8</v>
+      </c>
+      <c r="C62">
+        <v>90</v>
+      </c>
+      <c r="D62">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
       <c r="A63">
         <v>91</v>
       </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B63">
+        <v>91</v>
+      </c>
+      <c r="C63">
+        <v>92</v>
+      </c>
+      <c r="D63">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
       <c r="A64">
         <v>92</v>
       </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B64">
+        <v>91.8</v>
+      </c>
+      <c r="C64">
+        <v>93</v>
+      </c>
+      <c r="D64">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
       <c r="A65">
         <v>93</v>
       </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B65">
+        <v>92.9</v>
+      </c>
+      <c r="C65">
+        <v>94</v>
+      </c>
+      <c r="D65">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
       <c r="A66">
         <v>94</v>
       </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B66">
+        <v>93.9</v>
+      </c>
+      <c r="C66">
+        <v>94</v>
+      </c>
+      <c r="D66">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
       <c r="A67">
         <v>95</v>
       </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B67">
+        <v>95</v>
+      </c>
+      <c r="C67">
+        <v>96</v>
+      </c>
+      <c r="D67">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
       <c r="A68">
         <v>96</v>
       </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B68">
+        <v>95.9</v>
+      </c>
+      <c r="C68">
+        <v>97</v>
+      </c>
+      <c r="D68">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
       <c r="A69">
         <v>97</v>
       </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B69">
+        <v>96.7</v>
+      </c>
+      <c r="C69">
+        <v>98</v>
+      </c>
+      <c r="D69">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
       <c r="A70">
         <v>98</v>
       </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B70">
+        <v>97.9</v>
+      </c>
+      <c r="C70">
+        <v>98</v>
+      </c>
+      <c r="D70">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
       <c r="A71">
         <v>99</v>
       </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B71">
+        <v>99</v>
+      </c>
+      <c r="C71">
+        <v>99</v>
+      </c>
+      <c r="D71">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
       <c r="A72">
         <v>100</v>
       </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B72">
+        <v>99.9</v>
+      </c>
+      <c r="C72">
+        <v>100</v>
+      </c>
+      <c r="D72">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
       <c r="A73">
         <v>101</v>
       </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B73">
+        <v>100.9</v>
+      </c>
+      <c r="C73">
+        <v>101</v>
+      </c>
+      <c r="D73">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
       <c r="A74">
         <v>102</v>
       </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B74">
+        <v>102</v>
+      </c>
+      <c r="C74">
+        <v>102</v>
+      </c>
+      <c r="D74">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
       <c r="A75">
         <v>103</v>
       </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B75">
+        <v>102.8</v>
+      </c>
+      <c r="C75">
+        <v>103</v>
+      </c>
+      <c r="D75">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
       <c r="A76">
         <v>104</v>
       </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B76">
+        <v>103.7</v>
+      </c>
+      <c r="C76">
+        <v>104</v>
+      </c>
+      <c r="D76">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
       <c r="A77">
         <v>105</v>
       </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B77">
+        <v>104.8</v>
+      </c>
+      <c r="C77">
+        <v>105</v>
+      </c>
+      <c r="D77">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
       <c r="A78">
         <v>106</v>
       </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B78">
+        <v>105.8</v>
+      </c>
+      <c r="C78">
+        <v>106</v>
+      </c>
+      <c r="D78">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
       <c r="A79">
         <v>107</v>
       </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B79">
+        <v>107.1</v>
+      </c>
+      <c r="C79">
+        <v>107</v>
+      </c>
+      <c r="D79">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
       <c r="A80">
         <v>108</v>
       </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B80">
+        <v>108</v>
+      </c>
+      <c r="C80">
+        <v>108</v>
+      </c>
+      <c r="D80">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
       <c r="A81">
         <v>109</v>
       </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B81">
+        <v>108.9</v>
+      </c>
+      <c r="C81">
+        <v>109</v>
+      </c>
+      <c r="D81">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
       <c r="A82">
         <v>110</v>
+      </c>
+      <c r="B82">
+        <v>109.9</v>
+      </c>
+      <c r="C82">
+        <v>110</v>
+      </c>
+      <c r="D82">
+        <v>833</v>
       </c>
     </row>
   </sheetData>

--- a/dateTermistori.xlsx
+++ b/dateTermistori.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29912"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WIP\EVR\EVR_terminal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0AEC31C7-8AD3-4C4E-A8B7-0C05811DCF69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15E8F2A5-64C0-484F-967E-32C32220C8AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="7740" windowWidth="14610" windowHeight="7845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foaie1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Temp Pat</t>
   </si>
@@ -50,14 +50,17 @@
     <t>Medie ADC</t>
   </si>
   <si>
-    <t>Timp</t>
+    <t>MedieAdc_filtrat</t>
+  </si>
+  <si>
+    <t>ADC_ideal</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -368,16 +371,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E82"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:F82"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -393,8 +397,11 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>30</v>
       </c>
@@ -407,8 +414,14 @@
       <c r="D2">
         <v>2708</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="E2">
+        <v>2725.3</v>
+      </c>
+      <c r="F2">
+        <v>1824.7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>31</v>
       </c>
@@ -421,8 +434,14 @@
       <c r="D3">
         <v>2670</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="E3">
+        <v>2687.6</v>
+      </c>
+      <c r="F3">
+        <v>1781.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>32</v>
       </c>
@@ -435,8 +454,14 @@
       <c r="D4">
         <v>2640</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="E4">
+        <v>2658.4</v>
+      </c>
+      <c r="F4">
+        <v>1738.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>33</v>
       </c>
@@ -449,8 +474,14 @@
       <c r="D5">
         <v>2605</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="E5">
+        <v>2621.7</v>
+      </c>
+      <c r="F5">
+        <v>1696.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>34</v>
       </c>
@@ -463,8 +494,14 @@
       <c r="D6">
         <v>2575</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="E6">
+        <v>2593</v>
+      </c>
+      <c r="F6">
+        <v>1655</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>35</v>
       </c>
@@ -477,8 +514,14 @@
       <c r="D7">
         <v>2540</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="E7">
+        <v>2558.5</v>
+      </c>
+      <c r="F7">
+        <v>1614</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>36</v>
       </c>
@@ -491,8 +534,14 @@
       <c r="D8">
         <v>2505</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="E8">
+        <v>2521.3000000000002</v>
+      </c>
+      <c r="F8">
+        <v>1573.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>37</v>
       </c>
@@ -505,8 +554,14 @@
       <c r="D9">
         <v>2475</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="E9">
+        <v>2489.4</v>
+      </c>
+      <c r="F9">
+        <v>1533.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>38</v>
       </c>
@@ -519,8 +574,14 @@
       <c r="D10">
         <v>2440</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="E10">
+        <v>2456.1999999999998</v>
+      </c>
+      <c r="F10">
+        <v>1494.9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>39</v>
       </c>
@@ -533,8 +594,14 @@
       <c r="D11">
         <v>2405</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="E11">
+        <v>2422.3000000000002</v>
+      </c>
+      <c r="F11">
+        <v>1456.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>40</v>
       </c>
@@ -547,8 +614,14 @@
       <c r="D12">
         <v>2375</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="E12">
+        <v>2387.8000000000002</v>
+      </c>
+      <c r="F12">
+        <v>1418.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>41</v>
       </c>
@@ -561,8 +634,14 @@
       <c r="D13">
         <v>2350</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="E13">
+        <v>2362.8000000000002</v>
+      </c>
+      <c r="F13">
+        <v>1381.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>42</v>
       </c>
@@ -575,8 +654,14 @@
       <c r="D14">
         <v>2315</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="E14">
+        <v>2329</v>
+      </c>
+      <c r="F14">
+        <v>1345.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>43</v>
       </c>
@@ -589,8 +674,14 @@
       <c r="D15">
         <v>2280</v>
       </c>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="E15">
+        <v>2284.4</v>
+      </c>
+      <c r="F15">
+        <v>1309.9000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>44</v>
       </c>
@@ -603,8 +694,14 @@
       <c r="D16">
         <v>2235</v>
       </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="E16">
+        <v>2253.4</v>
+      </c>
+      <c r="F16">
+        <v>1275.0999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>45</v>
       </c>
@@ -617,8 +714,14 @@
       <c r="D17">
         <v>2205</v>
       </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="E17">
+        <v>2219.6999999999998</v>
+      </c>
+      <c r="F17">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>46</v>
       </c>
@@ -631,8 +734,14 @@
       <c r="D18">
         <v>2170</v>
       </c>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="E18">
+        <v>2185.1999999999998</v>
+      </c>
+      <c r="F18">
+        <v>1207.5999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>47</v>
       </c>
@@ -645,8 +754,14 @@
       <c r="D19">
         <v>2140</v>
       </c>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="E19">
+        <v>2154.3000000000002</v>
+      </c>
+      <c r="F19">
+        <v>1174.9000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>48</v>
       </c>
@@ -659,8 +774,14 @@
       <c r="D20">
         <v>2115</v>
       </c>
-    </row>
-    <row r="21" spans="1:4">
+      <c r="E20">
+        <v>2128.1999999999998</v>
+      </c>
+      <c r="F20">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>49</v>
       </c>
@@ -673,8 +794,14 @@
       <c r="D21">
         <v>2085</v>
       </c>
-    </row>
-    <row r="22" spans="1:4">
+      <c r="E21">
+        <v>2097.6</v>
+      </c>
+      <c r="F21">
+        <v>1111.8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>50</v>
       </c>
@@ -687,8 +814,14 @@
       <c r="D22">
         <v>2045</v>
       </c>
-    </row>
-    <row r="23" spans="1:4">
+      <c r="E22">
+        <v>2058.6</v>
+      </c>
+      <c r="F22">
+        <v>1081.4000000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>51</v>
       </c>
@@ -701,8 +834,14 @@
       <c r="D23">
         <v>2015</v>
       </c>
-    </row>
-    <row r="24" spans="1:4">
+      <c r="E23">
+        <v>2028.2</v>
+      </c>
+      <c r="F23">
+        <v>1051.5999999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>52</v>
       </c>
@@ -715,8 +854,14 @@
       <c r="D24">
         <v>1985</v>
       </c>
-    </row>
-    <row r="25" spans="1:4">
+      <c r="E24">
+        <v>1998.5</v>
+      </c>
+      <c r="F24">
+        <v>1022.6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>53</v>
       </c>
@@ -729,8 +874,14 @@
       <c r="D25">
         <v>1955</v>
       </c>
-    </row>
-    <row r="26" spans="1:4">
+      <c r="E25">
+        <v>1967.6</v>
+      </c>
+      <c r="F25">
+        <v>994.28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>54</v>
       </c>
@@ -743,8 +894,14 @@
       <c r="D26">
         <v>1930</v>
       </c>
-    </row>
-    <row r="27" spans="1:4">
+      <c r="E26">
+        <v>1938.7</v>
+      </c>
+      <c r="F26">
+        <v>966.67</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>55</v>
       </c>
@@ -757,8 +914,14 @@
       <c r="D27">
         <v>1900</v>
       </c>
-    </row>
-    <row r="28" spans="1:4">
+      <c r="E27">
+        <v>1909.9</v>
+      </c>
+      <c r="F27">
+        <v>939.77</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>56</v>
       </c>
@@ -771,8 +934,14 @@
       <c r="D28">
         <v>1875</v>
       </c>
-    </row>
-    <row r="29" spans="1:4">
+      <c r="E28">
+        <v>1884.2</v>
+      </c>
+      <c r="F28">
+        <v>913.55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>57</v>
       </c>
@@ -785,8 +954,14 @@
       <c r="D29">
         <v>1845</v>
       </c>
-    </row>
-    <row r="30" spans="1:4">
+      <c r="E29">
+        <v>1854.7</v>
+      </c>
+      <c r="F29">
+        <v>888.01</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>58</v>
       </c>
@@ -799,8 +974,14 @@
       <c r="D30">
         <v>1815</v>
       </c>
-    </row>
-    <row r="31" spans="1:4">
+      <c r="E30">
+        <v>1826.4</v>
+      </c>
+      <c r="F30">
+        <v>863.14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>59</v>
       </c>
@@ -813,8 +994,14 @@
       <c r="D31">
         <v>1790</v>
       </c>
-    </row>
-    <row r="32" spans="1:4">
+      <c r="E31">
+        <v>1798.6</v>
+      </c>
+      <c r="F31">
+        <v>838.93</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>60</v>
       </c>
@@ -827,8 +1014,14 @@
       <c r="D32">
         <v>1760</v>
       </c>
-    </row>
-    <row r="33" spans="1:4">
+      <c r="E32">
+        <v>1771.3</v>
+      </c>
+      <c r="F32">
+        <v>815.37</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>61</v>
       </c>
@@ -841,8 +1034,14 @@
       <c r="D33">
         <v>1735</v>
       </c>
-    </row>
-    <row r="34" spans="1:4">
+      <c r="E33">
+        <v>1744.6</v>
+      </c>
+      <c r="F33">
+        <v>792.45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>62</v>
       </c>
@@ -855,8 +1054,14 @@
       <c r="D34">
         <v>1705</v>
       </c>
-    </row>
-    <row r="35" spans="1:4">
+      <c r="E34">
+        <v>1714.9</v>
+      </c>
+      <c r="F34">
+        <v>770.15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>63</v>
       </c>
@@ -869,8 +1074,14 @@
       <c r="D35">
         <v>1680</v>
       </c>
-    </row>
-    <row r="36" spans="1:4">
+      <c r="E35">
+        <v>1689.1</v>
+      </c>
+      <c r="F35">
+        <v>748.46</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>64</v>
       </c>
@@ -883,8 +1094,14 @@
       <c r="D36">
         <v>1655</v>
       </c>
-    </row>
-    <row r="37" spans="1:4">
+      <c r="E36">
+        <v>1661.8</v>
+      </c>
+      <c r="F36">
+        <v>727.38</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>65</v>
       </c>
@@ -897,8 +1114,14 @@
       <c r="D37">
         <v>1630</v>
       </c>
-    </row>
-    <row r="38" spans="1:4">
+      <c r="E37">
+        <v>1637.4</v>
+      </c>
+      <c r="F37">
+        <v>706.89</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>66</v>
       </c>
@@ -911,8 +1134,14 @@
       <c r="D38">
         <v>1607</v>
       </c>
-    </row>
-    <row r="39" spans="1:4">
+      <c r="E38">
+        <v>1611.2</v>
+      </c>
+      <c r="F38">
+        <v>686.97</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>67</v>
       </c>
@@ -925,8 +1154,14 @@
       <c r="D39">
         <v>1580</v>
       </c>
-    </row>
-    <row r="40" spans="1:4">
+      <c r="E39">
+        <v>1587.3</v>
+      </c>
+      <c r="F39">
+        <v>667.62</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>68</v>
       </c>
@@ -939,8 +1174,14 @@
       <c r="D40">
         <v>1558</v>
       </c>
-    </row>
-    <row r="41" spans="1:4">
+      <c r="E40">
+        <v>1566.2</v>
+      </c>
+      <c r="F40">
+        <v>648.80999999999995</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>69</v>
       </c>
@@ -953,8 +1194,14 @@
       <c r="D41">
         <v>1533</v>
       </c>
-    </row>
-    <row r="42" spans="1:4">
+      <c r="E41">
+        <v>1532.8</v>
+      </c>
+      <c r="F41">
+        <v>630.54999999999995</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>70</v>
       </c>
@@ -967,8 +1214,14 @@
       <c r="D42">
         <v>1486</v>
       </c>
-    </row>
-    <row r="43" spans="1:4">
+      <c r="E42">
+        <v>1510.7</v>
+      </c>
+      <c r="F42">
+        <v>612.80999999999995</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>71</v>
       </c>
@@ -981,8 +1234,14 @@
       <c r="D43">
         <v>1463</v>
       </c>
-    </row>
-    <row r="44" spans="1:4">
+      <c r="E43">
+        <v>1459.9</v>
+      </c>
+      <c r="F43">
+        <v>595.58000000000004</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>72</v>
       </c>
@@ -995,8 +1254,14 @@
       <c r="D44">
         <v>1419</v>
       </c>
-    </row>
-    <row r="45" spans="1:4">
+      <c r="E44">
+        <v>1432.8</v>
+      </c>
+      <c r="F44">
+        <v>578.86</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>73</v>
       </c>
@@ -1009,8 +1274,14 @@
       <c r="D45">
         <v>1382</v>
       </c>
-    </row>
-    <row r="46" spans="1:4">
+      <c r="E45">
+        <v>1401.1</v>
+      </c>
+      <c r="F45">
+        <v>562.62</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>74</v>
       </c>
@@ -1023,8 +1294,14 @@
       <c r="D46">
         <v>1304</v>
       </c>
-    </row>
-    <row r="47" spans="1:4">
+      <c r="E46">
+        <v>1386.2</v>
+      </c>
+      <c r="F46">
+        <v>546.85</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>75</v>
       </c>
@@ -1037,8 +1314,14 @@
       <c r="D47">
         <v>1365</v>
       </c>
-    </row>
-    <row r="48" spans="1:4">
+      <c r="E47">
+        <v>1317.8</v>
+      </c>
+      <c r="F47">
+        <v>531.54999999999995</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>76</v>
       </c>
@@ -1051,8 +1334,14 @@
       <c r="D48">
         <v>1270</v>
       </c>
-    </row>
-    <row r="49" spans="1:4">
+      <c r="E48">
+        <v>1279.5999999999999</v>
+      </c>
+      <c r="F48">
+        <v>516.70000000000005</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>77</v>
       </c>
@@ -1065,8 +1354,14 @@
       <c r="D49">
         <v>1255</v>
       </c>
-    </row>
-    <row r="50" spans="1:4">
+      <c r="E49">
+        <v>1255.2</v>
+      </c>
+      <c r="F49">
+        <v>502.29</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>78</v>
       </c>
@@ -1079,8 +1374,14 @@
       <c r="D50">
         <v>1227</v>
       </c>
-    </row>
-    <row r="51" spans="1:4">
+      <c r="E50">
+        <v>1226.5999999999999</v>
+      </c>
+      <c r="F50">
+        <v>488.3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>79</v>
       </c>
@@ -1093,8 +1394,14 @@
       <c r="D51">
         <v>1174</v>
       </c>
-    </row>
-    <row r="52" spans="1:4">
+      <c r="E51">
+        <v>1177.4000000000001</v>
+      </c>
+      <c r="F51">
+        <v>474.73</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>80</v>
       </c>
@@ -1107,8 +1414,14 @@
       <c r="D52">
         <v>1158</v>
       </c>
-    </row>
-    <row r="53" spans="1:4">
+      <c r="E52">
+        <v>1161.2</v>
+      </c>
+      <c r="F52">
+        <v>461.56</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>81</v>
       </c>
@@ -1121,8 +1434,14 @@
       <c r="D53">
         <v>1133</v>
       </c>
-    </row>
-    <row r="54" spans="1:4">
+      <c r="E53">
+        <v>1134.9000000000001</v>
+      </c>
+      <c r="F53">
+        <v>448.79</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>82</v>
       </c>
@@ -1135,8 +1454,14 @@
       <c r="D54">
         <v>1119</v>
       </c>
-    </row>
-    <row r="55" spans="1:4">
+      <c r="E54">
+        <v>1121.7</v>
+      </c>
+      <c r="F54">
+        <v>436.39</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>83</v>
       </c>
@@ -1149,8 +1474,14 @@
       <c r="D55">
         <v>1106</v>
       </c>
-    </row>
-    <row r="56" spans="1:4">
+      <c r="E55">
+        <v>1108.5</v>
+      </c>
+      <c r="F55">
+        <v>424.36</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>84</v>
       </c>
@@ -1163,8 +1494,14 @@
       <c r="D56">
         <v>1095</v>
       </c>
-    </row>
-    <row r="57" spans="1:4">
+      <c r="E56">
+        <v>1097.5999999999999</v>
+      </c>
+      <c r="F56">
+        <v>412.69</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>85</v>
       </c>
@@ -1177,8 +1514,14 @@
       <c r="D57">
         <v>1082</v>
       </c>
-    </row>
-    <row r="58" spans="1:4">
+      <c r="E57">
+        <v>1083.8</v>
+      </c>
+      <c r="F57">
+        <v>401.38</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>86</v>
       </c>
@@ -1191,8 +1534,14 @@
       <c r="D58">
         <v>1072</v>
       </c>
-    </row>
-    <row r="59" spans="1:4">
+      <c r="E58">
+        <v>1074.9000000000001</v>
+      </c>
+      <c r="F58">
+        <v>390.39</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>87</v>
       </c>
@@ -1205,8 +1554,14 @@
       <c r="D59">
         <v>1061</v>
       </c>
-    </row>
-    <row r="60" spans="1:4">
+      <c r="E59">
+        <v>1063.3</v>
+      </c>
+      <c r="F59">
+        <v>379.74</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>88</v>
       </c>
@@ -1219,8 +1574,14 @@
       <c r="D60">
         <v>1050</v>
       </c>
-    </row>
-    <row r="61" spans="1:4">
+      <c r="E60">
+        <v>1052.2</v>
+      </c>
+      <c r="F60">
+        <v>369.41</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>89</v>
       </c>
@@ -1233,8 +1594,14 @@
       <c r="D61">
         <v>1037</v>
       </c>
-    </row>
-    <row r="62" spans="1:4">
+      <c r="E61">
+        <v>1040.2</v>
+      </c>
+      <c r="F61">
+        <v>359.38</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>90</v>
       </c>
@@ -1247,8 +1614,14 @@
       <c r="D62">
         <v>1023</v>
       </c>
-    </row>
-    <row r="63" spans="1:4">
+      <c r="E62">
+        <v>1025.3</v>
+      </c>
+      <c r="F62">
+        <v>349.66</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>91</v>
       </c>
@@ -1261,8 +1634,14 @@
       <c r="D63">
         <v>1014</v>
       </c>
-    </row>
-    <row r="64" spans="1:4">
+      <c r="E63">
+        <v>1016.1</v>
+      </c>
+      <c r="F63">
+        <v>340.22</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>92</v>
       </c>
@@ -1275,8 +1654,14 @@
       <c r="D64">
         <v>1002</v>
       </c>
-    </row>
-    <row r="65" spans="1:4">
+      <c r="E64">
+        <v>1005.8</v>
+      </c>
+      <c r="F64">
+        <v>331.07</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>93</v>
       </c>
@@ -1289,8 +1674,14 @@
       <c r="D65">
         <v>992</v>
       </c>
-    </row>
-    <row r="66" spans="1:4">
+      <c r="E65">
+        <v>995.61</v>
+      </c>
+      <c r="F65">
+        <v>322.19</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>94</v>
       </c>
@@ -1303,8 +1694,14 @@
       <c r="D66">
         <v>981</v>
       </c>
-    </row>
-    <row r="67" spans="1:4">
+      <c r="E66">
+        <v>983.24</v>
+      </c>
+      <c r="F66">
+        <v>313.57</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>95</v>
       </c>
@@ -1317,8 +1714,14 @@
       <c r="D67">
         <v>970</v>
       </c>
-    </row>
-    <row r="68" spans="1:4">
+      <c r="E67">
+        <v>972.46</v>
+      </c>
+      <c r="F67">
+        <v>305.22000000000003</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>96</v>
       </c>
@@ -1331,8 +1734,14 @@
       <c r="D68">
         <v>960</v>
       </c>
-    </row>
-    <row r="69" spans="1:4">
+      <c r="E68">
+        <v>963.86</v>
+      </c>
+      <c r="F68">
+        <v>297.11</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>97</v>
       </c>
@@ -1345,8 +1754,14 @@
       <c r="D69">
         <v>950</v>
       </c>
-    </row>
-    <row r="70" spans="1:4">
+      <c r="E69">
+        <v>953.79</v>
+      </c>
+      <c r="F69">
+        <v>289.24</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>98</v>
       </c>
@@ -1359,8 +1774,14 @@
       <c r="D70">
         <v>941</v>
       </c>
-    </row>
-    <row r="71" spans="1:4">
+      <c r="E70">
+        <v>943.54</v>
+      </c>
+      <c r="F70">
+        <v>281.61</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>99</v>
       </c>
@@ -1373,8 +1794,14 @@
       <c r="D71">
         <v>929</v>
       </c>
-    </row>
-    <row r="72" spans="1:4">
+      <c r="E71">
+        <v>932.31</v>
+      </c>
+      <c r="F71">
+        <v>274.2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>100</v>
       </c>
@@ -1387,8 +1814,14 @@
       <c r="D72">
         <v>920</v>
       </c>
-    </row>
-    <row r="73" spans="1:4">
+      <c r="E72">
+        <v>922.86</v>
+      </c>
+      <c r="F72">
+        <v>267.01</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>101</v>
       </c>
@@ -1401,8 +1834,14 @@
       <c r="D73">
         <v>911</v>
       </c>
-    </row>
-    <row r="74" spans="1:4">
+      <c r="E73">
+        <v>913.54</v>
+      </c>
+      <c r="F73">
+        <v>260.02999999999997</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>102</v>
       </c>
@@ -1415,8 +1854,14 @@
       <c r="D74">
         <v>900</v>
       </c>
-    </row>
-    <row r="75" spans="1:4">
+      <c r="E74">
+        <v>902.67</v>
+      </c>
+      <c r="F74">
+        <v>253.26</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>103</v>
       </c>
@@ -1429,8 +1874,14 @@
       <c r="D75">
         <v>891</v>
       </c>
-    </row>
-    <row r="76" spans="1:4">
+      <c r="E75">
+        <v>894.42</v>
+      </c>
+      <c r="F75">
+        <v>246.7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>104</v>
       </c>
@@ -1443,8 +1894,14 @@
       <c r="D76">
         <v>883</v>
       </c>
-    </row>
-    <row r="77" spans="1:4">
+      <c r="E76">
+        <v>886.29</v>
+      </c>
+      <c r="F76">
+        <v>240.32</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>105</v>
       </c>
@@ -1457,8 +1914,14 @@
       <c r="D77">
         <v>873</v>
       </c>
-    </row>
-    <row r="78" spans="1:4">
+      <c r="E77">
+        <v>876.4</v>
+      </c>
+      <c r="F77">
+        <v>234.13</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>106</v>
       </c>
@@ -1471,8 +1934,14 @@
       <c r="D78">
         <v>864</v>
       </c>
-    </row>
-    <row r="79" spans="1:4">
+      <c r="E78">
+        <v>867.89</v>
+      </c>
+      <c r="F78">
+        <v>228.12</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>107</v>
       </c>
@@ -1485,8 +1954,14 @@
       <c r="D79">
         <v>856</v>
       </c>
-    </row>
-    <row r="80" spans="1:4">
+      <c r="E79">
+        <v>859.74</v>
+      </c>
+      <c r="F79">
+        <v>222.29</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>108</v>
       </c>
@@ -1499,8 +1974,14 @@
       <c r="D80">
         <v>849</v>
       </c>
-    </row>
-    <row r="81" spans="1:4">
+      <c r="E80">
+        <v>852</v>
+      </c>
+      <c r="F80">
+        <v>216.63</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>109</v>
       </c>
@@ -1513,8 +1994,14 @@
       <c r="D81">
         <v>841</v>
       </c>
-    </row>
-    <row r="82" spans="1:4">
+      <c r="E81">
+        <v>843.72</v>
+      </c>
+      <c r="F81">
+        <v>211.13</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>110</v>
       </c>
@@ -1526,6 +2013,12 @@
       </c>
       <c r="D82">
         <v>833</v>
+      </c>
+      <c r="E82">
+        <v>836.18</v>
+      </c>
+      <c r="F82">
+        <v>205.79</v>
       </c>
     </row>
   </sheetData>

--- a/dateTermistori.xlsx
+++ b/dateTermistori.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WIP\EVR\EVR_terminal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15E8F2A5-64C0-484F-967E-32C32220C8AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A67C5F8C-9875-4F36-9D64-1E648738C75D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Foaie1" sheetId="1" r:id="rId1"/>
+    <sheet name="dateBrute" sheetId="1" r:id="rId1"/>
+    <sheet name="LUT" sheetId="3" r:id="rId2"/>
+    <sheet name="grafice" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>Temp Pat</t>
   </si>
@@ -54,6 +56,21 @@
   </si>
   <si>
     <t>ADC_ideal</t>
+  </si>
+  <si>
+    <t>Abatere real_ideal</t>
+  </si>
+  <si>
+    <t>Diferenta Ideal</t>
+  </si>
+  <si>
+    <t>Diferenta real</t>
+  </si>
+  <si>
+    <t>ADC</t>
+  </si>
+  <si>
+    <t>=</t>
   </si>
 </sst>
 </file>
@@ -106,6 +123,6660 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ro-RO"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>ADC_ideal vs Temp</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>dateBrute!$A$2:$A$82</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="81"/>
+                <c:pt idx="0">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>101</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>106</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>109</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>110</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>dateBrute!$G$2:$G$82</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="81"/>
+                <c:pt idx="0">
+                  <c:v>1824.7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1781.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1738.7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1696.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1655</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1614</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1573.7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1533.9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1494.9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1456.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1418.8</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1381.8</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1345.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1309.9000000000001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1275.0999999999999</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1241</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1207.5999999999999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1174.9000000000001</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1143</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1111.8</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1081.4000000000001</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1051.5999999999999</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1022.6</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>994.28</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>966.67</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>939.77</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>913.55</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>888.01</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>863.14</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>838.93</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>815.37</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>792.45</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>770.15</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>748.46</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>727.38</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>706.89</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>686.97</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>667.62</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>648.80999999999995</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>630.54999999999995</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>612.80999999999995</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>595.58000000000004</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>578.86</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>562.62</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>546.85</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>531.54999999999995</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>516.70000000000005</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>502.29</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>488.3</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>474.73</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>461.56</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>448.79</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>436.39</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>424.36</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>412.69</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>401.38</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>390.39</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>379.74</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>369.41</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>359.38</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>349.66</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>340.22</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>331.07</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>322.19</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>313.57</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>305.22000000000003</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>297.11</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>289.24</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>281.61</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>274.2</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>267.01</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>260.02999999999997</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>253.26</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>246.7</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>240.32</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>234.13</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>228.12</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>222.29</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>216.63</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>211.13</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>205.79</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0DC6-4DE0-AFEB-375C8BE743A7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1375970896"/>
+        <c:axId val="1375968976"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="0"/>
+                <c:order val="0"/>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="none"/>
+                </c:marker>
+                <c:cat>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>dateBrute!$A$2:$A$82</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="81"/>
+                      <c:pt idx="0">
+                        <c:v>30</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>31</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>32</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>33</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>34</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>35</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>36</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>37</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>38</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>39</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>40</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>41</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>42</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>43</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>44</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>45</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>46</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>47</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>48</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>49</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>50</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>51</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>52</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>53</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>54</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>55</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>56</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>57</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>58</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>59</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>60</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>61</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>62</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>63</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>64</c:v>
+                      </c:pt>
+                      <c:pt idx="35">
+                        <c:v>65</c:v>
+                      </c:pt>
+                      <c:pt idx="36">
+                        <c:v>66</c:v>
+                      </c:pt>
+                      <c:pt idx="37">
+                        <c:v>67</c:v>
+                      </c:pt>
+                      <c:pt idx="38">
+                        <c:v>68</c:v>
+                      </c:pt>
+                      <c:pt idx="39">
+                        <c:v>69</c:v>
+                      </c:pt>
+                      <c:pt idx="40">
+                        <c:v>70</c:v>
+                      </c:pt>
+                      <c:pt idx="41">
+                        <c:v>71</c:v>
+                      </c:pt>
+                      <c:pt idx="42">
+                        <c:v>72</c:v>
+                      </c:pt>
+                      <c:pt idx="43">
+                        <c:v>73</c:v>
+                      </c:pt>
+                      <c:pt idx="44">
+                        <c:v>74</c:v>
+                      </c:pt>
+                      <c:pt idx="45">
+                        <c:v>75</c:v>
+                      </c:pt>
+                      <c:pt idx="46">
+                        <c:v>76</c:v>
+                      </c:pt>
+                      <c:pt idx="47">
+                        <c:v>77</c:v>
+                      </c:pt>
+                      <c:pt idx="48">
+                        <c:v>78</c:v>
+                      </c:pt>
+                      <c:pt idx="49">
+                        <c:v>79</c:v>
+                      </c:pt>
+                      <c:pt idx="50">
+                        <c:v>80</c:v>
+                      </c:pt>
+                      <c:pt idx="51">
+                        <c:v>81</c:v>
+                      </c:pt>
+                      <c:pt idx="52">
+                        <c:v>82</c:v>
+                      </c:pt>
+                      <c:pt idx="53">
+                        <c:v>83</c:v>
+                      </c:pt>
+                      <c:pt idx="54">
+                        <c:v>84</c:v>
+                      </c:pt>
+                      <c:pt idx="55">
+                        <c:v>85</c:v>
+                      </c:pt>
+                      <c:pt idx="56">
+                        <c:v>86</c:v>
+                      </c:pt>
+                      <c:pt idx="57">
+                        <c:v>87</c:v>
+                      </c:pt>
+                      <c:pt idx="58">
+                        <c:v>88</c:v>
+                      </c:pt>
+                      <c:pt idx="59">
+                        <c:v>89</c:v>
+                      </c:pt>
+                      <c:pt idx="60">
+                        <c:v>90</c:v>
+                      </c:pt>
+                      <c:pt idx="61">
+                        <c:v>91</c:v>
+                      </c:pt>
+                      <c:pt idx="62">
+                        <c:v>92</c:v>
+                      </c:pt>
+                      <c:pt idx="63">
+                        <c:v>93</c:v>
+                      </c:pt>
+                      <c:pt idx="64">
+                        <c:v>94</c:v>
+                      </c:pt>
+                      <c:pt idx="65">
+                        <c:v>95</c:v>
+                      </c:pt>
+                      <c:pt idx="66">
+                        <c:v>96</c:v>
+                      </c:pt>
+                      <c:pt idx="67">
+                        <c:v>97</c:v>
+                      </c:pt>
+                      <c:pt idx="68">
+                        <c:v>98</c:v>
+                      </c:pt>
+                      <c:pt idx="69">
+                        <c:v>99</c:v>
+                      </c:pt>
+                      <c:pt idx="70">
+                        <c:v>100</c:v>
+                      </c:pt>
+                      <c:pt idx="71">
+                        <c:v>101</c:v>
+                      </c:pt>
+                      <c:pt idx="72">
+                        <c:v>102</c:v>
+                      </c:pt>
+                      <c:pt idx="73">
+                        <c:v>103</c:v>
+                      </c:pt>
+                      <c:pt idx="74">
+                        <c:v>104</c:v>
+                      </c:pt>
+                      <c:pt idx="75">
+                        <c:v>105</c:v>
+                      </c:pt>
+                      <c:pt idx="76">
+                        <c:v>106</c:v>
+                      </c:pt>
+                      <c:pt idx="77">
+                        <c:v>107</c:v>
+                      </c:pt>
+                      <c:pt idx="78">
+                        <c:v>108</c:v>
+                      </c:pt>
+                      <c:pt idx="79">
+                        <c:v>109</c:v>
+                      </c:pt>
+                      <c:pt idx="80">
+                        <c:v>110</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>dateBrute!$A$2:$A$82</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="81"/>
+                      <c:pt idx="0">
+                        <c:v>30</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>31</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>32</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>33</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>34</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>35</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>36</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>37</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>38</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>39</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>40</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>41</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>42</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>43</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>44</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>45</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>46</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>47</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>48</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>49</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>50</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>51</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>52</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>53</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>54</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>55</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>56</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>57</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>58</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>59</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>60</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>61</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>62</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>63</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>64</c:v>
+                      </c:pt>
+                      <c:pt idx="35">
+                        <c:v>65</c:v>
+                      </c:pt>
+                      <c:pt idx="36">
+                        <c:v>66</c:v>
+                      </c:pt>
+                      <c:pt idx="37">
+                        <c:v>67</c:v>
+                      </c:pt>
+                      <c:pt idx="38">
+                        <c:v>68</c:v>
+                      </c:pt>
+                      <c:pt idx="39">
+                        <c:v>69</c:v>
+                      </c:pt>
+                      <c:pt idx="40">
+                        <c:v>70</c:v>
+                      </c:pt>
+                      <c:pt idx="41">
+                        <c:v>71</c:v>
+                      </c:pt>
+                      <c:pt idx="42">
+                        <c:v>72</c:v>
+                      </c:pt>
+                      <c:pt idx="43">
+                        <c:v>73</c:v>
+                      </c:pt>
+                      <c:pt idx="44">
+                        <c:v>74</c:v>
+                      </c:pt>
+                      <c:pt idx="45">
+                        <c:v>75</c:v>
+                      </c:pt>
+                      <c:pt idx="46">
+                        <c:v>76</c:v>
+                      </c:pt>
+                      <c:pt idx="47">
+                        <c:v>77</c:v>
+                      </c:pt>
+                      <c:pt idx="48">
+                        <c:v>78</c:v>
+                      </c:pt>
+                      <c:pt idx="49">
+                        <c:v>79</c:v>
+                      </c:pt>
+                      <c:pt idx="50">
+                        <c:v>80</c:v>
+                      </c:pt>
+                      <c:pt idx="51">
+                        <c:v>81</c:v>
+                      </c:pt>
+                      <c:pt idx="52">
+                        <c:v>82</c:v>
+                      </c:pt>
+                      <c:pt idx="53">
+                        <c:v>83</c:v>
+                      </c:pt>
+                      <c:pt idx="54">
+                        <c:v>84</c:v>
+                      </c:pt>
+                      <c:pt idx="55">
+                        <c:v>85</c:v>
+                      </c:pt>
+                      <c:pt idx="56">
+                        <c:v>86</c:v>
+                      </c:pt>
+                      <c:pt idx="57">
+                        <c:v>87</c:v>
+                      </c:pt>
+                      <c:pt idx="58">
+                        <c:v>88</c:v>
+                      </c:pt>
+                      <c:pt idx="59">
+                        <c:v>89</c:v>
+                      </c:pt>
+                      <c:pt idx="60">
+                        <c:v>90</c:v>
+                      </c:pt>
+                      <c:pt idx="61">
+                        <c:v>91</c:v>
+                      </c:pt>
+                      <c:pt idx="62">
+                        <c:v>92</c:v>
+                      </c:pt>
+                      <c:pt idx="63">
+                        <c:v>93</c:v>
+                      </c:pt>
+                      <c:pt idx="64">
+                        <c:v>94</c:v>
+                      </c:pt>
+                      <c:pt idx="65">
+                        <c:v>95</c:v>
+                      </c:pt>
+                      <c:pt idx="66">
+                        <c:v>96</c:v>
+                      </c:pt>
+                      <c:pt idx="67">
+                        <c:v>97</c:v>
+                      </c:pt>
+                      <c:pt idx="68">
+                        <c:v>98</c:v>
+                      </c:pt>
+                      <c:pt idx="69">
+                        <c:v>99</c:v>
+                      </c:pt>
+                      <c:pt idx="70">
+                        <c:v>100</c:v>
+                      </c:pt>
+                      <c:pt idx="71">
+                        <c:v>101</c:v>
+                      </c:pt>
+                      <c:pt idx="72">
+                        <c:v>102</c:v>
+                      </c:pt>
+                      <c:pt idx="73">
+                        <c:v>103</c:v>
+                      </c:pt>
+                      <c:pt idx="74">
+                        <c:v>104</c:v>
+                      </c:pt>
+                      <c:pt idx="75">
+                        <c:v>105</c:v>
+                      </c:pt>
+                      <c:pt idx="76">
+                        <c:v>106</c:v>
+                      </c:pt>
+                      <c:pt idx="77">
+                        <c:v>107</c:v>
+                      </c:pt>
+                      <c:pt idx="78">
+                        <c:v>108</c:v>
+                      </c:pt>
+                      <c:pt idx="79">
+                        <c:v>109</c:v>
+                      </c:pt>
+                      <c:pt idx="80">
+                        <c:v>110</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000001-0DC6-4DE0-AFEB-375C8BE743A7}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+          </c:ext>
+        </c:extLst>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1375970896"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1375968976"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1375968976"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1375970896"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ro-RO"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>ADC_citit vs temp</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>dateBrute!$A$2:$A$82</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="81"/>
+                <c:pt idx="0">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>101</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>106</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>109</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>110</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>dateBrute!$E$2:$E$82</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="81"/>
+                <c:pt idx="0">
+                  <c:v>2725.3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2687.6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2658.4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2621.7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2593</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2558.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2521.3000000000002</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2489.4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2456.1999999999998</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2422.3000000000002</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2387.8000000000002</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2362.8000000000002</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2329</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2284.4</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2253.4</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2219.6999999999998</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2185.1999999999998</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2154.3000000000002</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2128.1999999999998</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2097.6</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2058.6</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2028.2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1998.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1967.6</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1938.7</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1909.9</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1884.2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1854.7</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1826.4</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1798.6</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1771.3</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1744.6</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1714.9</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1689.1</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1661.8</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1637.4</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1611.2</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1587.3</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1566.2</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1532.8</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1510.7</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1459.9</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1432.8</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1401.1</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1386.2</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1317.8</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1279.5999999999999</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1255.2</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1226.5999999999999</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1177.4000000000001</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1161.2</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>1134.9000000000001</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>1121.7</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>1108.5</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1097.5999999999999</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1083.8</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1074.9000000000001</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1063.3</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1052.2</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1040.2</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1025.3</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1016.1</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1005.8</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>995.61</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>983.24</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>972.46</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>963.86</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>953.79</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>943.54</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>932.31</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>922.86</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>913.54</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>902.67</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>894.42</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>886.29</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>876.4</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>867.89</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>859.74</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>852</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>843.72</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>836.18</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2613-42CA-9DDB-1B6E2A0CFD5F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1914983360"/>
+        <c:axId val="1914983840"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1914983360"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1914983840"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1914983840"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1914983360"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ro-RO"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>dateBrute!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Diferenta real</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>dateBrute!$A$2:$A$82</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="81"/>
+                <c:pt idx="0">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>101</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>106</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>109</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>110</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>dateBrute!$F$2:$F$83</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="82"/>
+                <c:pt idx="1">
+                  <c:v>37.700000000000273</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>29.199999999999818</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>36.700000000000273</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>28.699999999999818</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>34.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>37.199999999999818</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>31.900000000000091</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>33.200000000000273</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>33.899999999999636</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>34.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>33.800000000000182</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>44.599999999999909</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>33.700000000000273</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>34.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>30.899999999999636</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>26.100000000000364</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>30.599999999999909</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>30.399999999999864</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>29.700000000000045</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>30.900000000000091</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>28.899999999999864</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>28.799999999999955</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>25.700000000000045</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>29.5</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>28.299999999999955</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>27.800000000000182</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>27.299999999999955</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>26.700000000000045</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>29.699999999999818</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>25.800000000000182</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>27.299999999999955</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>24.399999999999864</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>26.200000000000045</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>23.900000000000091</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>21.099999999999909</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>33.400000000000091</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>22.099999999999909</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>50.799999999999955</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>27.100000000000136</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>31.700000000000045</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>14.899999999999864</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>68.400000000000091</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>38.200000000000045</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>24.399999999999864</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>28.600000000000136</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>49.199999999999818</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>16.200000000000045</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>26.299999999999955</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>13.200000000000045</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>13.200000000000045</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>10.900000000000091</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>13.799999999999955</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>8.8999999999998636</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>11.600000000000136</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>11.099999999999909</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>14.900000000000091</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>9.1999999999999318</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>10.300000000000068</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>10.189999999999941</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>12.370000000000005</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>10.779999999999973</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>8.6000000000000227</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>10.07000000000005</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>10.25</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>11.230000000000018</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>9.4499999999999318</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>9.32000000000005</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>10.870000000000005</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>8.25</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>8.1299999999999955</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>9.8899999999999864</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>8.5099999999999909</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>8.1499999999999773</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>7.7400000000000091</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>8.2799999999999727</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>7.5400000000000773</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-AEB5-4744-8D59-5E8D99F178E3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>dateBrute!$H$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Diferenta Ideal</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>dateBrute!$A$2:$A$82</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="81"/>
+                <c:pt idx="0">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>101</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>106</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>109</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>110</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>dateBrute!$H$2:$H$83</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="82"/>
+                <c:pt idx="1">
+                  <c:v>43.200000000000045</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>42.799999999999955</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>42.100000000000136</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>41.599999999999909</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>40.299999999999955</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>39.799999999999955</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>38.400000000000091</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>37.700000000000045</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>36.299999999999955</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>35.599999999999909</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>34.800000000000182</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>34.099999999999909</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>33.400000000000091</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>32.699999999999818</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>31.900000000000091</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>31.200000000000045</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>30.399999999999864</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>29.800000000000182</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>28.999999999999886</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>28.32000000000005</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>27.610000000000014</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26.899999999999977</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>26.220000000000027</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>25.539999999999964</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>24.870000000000005</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>24.210000000000036</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>23.559999999999945</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>22.919999999999959</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>22.300000000000068</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>21.689999999999941</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>21.080000000000041</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>20.490000000000009</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>19.919999999999959</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>19.350000000000023</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>18.810000000000059</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>18.259999999999991</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>17.740000000000009</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>17.229999999999905</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>16.720000000000027</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>16.240000000000009</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>15.769999999999982</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>15.300000000000068</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>14.849999999999909</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>14.410000000000025</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>13.990000000000009</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>13.569999999999993</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>13.170000000000016</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>12.769999999999982</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>12.400000000000034</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>12.029999999999973</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>11.670000000000016</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>11.310000000000002</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>10.990000000000009</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>10.649999999999977</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>10.329999999999984</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>10.03000000000003</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>9.7199999999999704</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>9.4399999999999977</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>9.1500000000000341</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>8.8799999999999955</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>8.6200000000000045</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>8.3499999999999659</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>8.1100000000000136</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>7.8700000000000045</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>7.6299999999999955</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>7.410000000000025</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>7.1899999999999977</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>6.9800000000000182</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>6.7699999999999818</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>6.5600000000000023</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>6.3799999999999955</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>6.1899999999999977</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>6.0099999999999909</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>5.8300000000000125</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>5.6599999999999966</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>5.3400000000000034</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-AEB5-4744-8D59-5E8D99F178E3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1927216384"/>
+        <c:axId val="1927216864"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1927216384"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1927216864"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1927216864"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1927216384"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:userShapes r:id="rId3"/>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ro-RO"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>dateBrute!$I$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Abatere real_ideal</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>dateBrute!$A$2:$A$82</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="81"/>
+                <c:pt idx="0">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>101</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>106</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>109</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>110</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>dateBrute!$I$2:$I$82</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="81"/>
+                <c:pt idx="0">
+                  <c:v>883.3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>888.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>901.3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>908.40000000000009</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>920</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>926</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>931.3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>941.09999999999991</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>945.09999999999991</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>948.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>956.2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>968.2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>969.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>970.09999999999991</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>959.90000000000009</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>964</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>962.40000000000009</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>965.09999999999991</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>972</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>973.2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>963.59999999999991</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>963.40000000000009</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>962.4</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>960.72</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>963.33</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>960.23</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>961.45</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>956.99</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>951.86</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>951.07</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>944.63</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>942.55</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>934.85</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>931.54</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>927.62</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>923.11</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>920.03</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>912.38</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>909.19</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>902.45</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>873.19</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>867.42</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>840.14</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>819.38</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>757.15</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>833.45</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>753.3</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>752.71</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>738.7</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>699.27</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>696.44</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>684.21</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>682.61</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>681.64</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>682.31</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>680.62</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>681.61</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>681.26</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>680.58999999999992</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>677.62</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>673.33999999999992</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>673.78</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>670.93000000000006</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>669.81</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>667.43000000000006</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>664.78</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>662.89</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>660.76</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>659.39</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>654.79999999999995</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>652.99</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>650.97</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>646.74</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>644.29999999999995</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>642.68000000000006</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>638.87</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>635.88</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>633.71</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>632.37</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>629.87</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>627.21</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6DC8-4C66-8E59-CECD22FB0FCA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1927195744"/>
+        <c:axId val="1927202944"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1927195744"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1927202944"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1927202944"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1927195744"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Diagramă 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{569A252A-83E2-45F2-B28C-CD61B7C83AAF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>80961</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>47624</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Diagramă 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B53E9CE-2001-4DE9-97A3-34662E4A395B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>428624</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>342899</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Diagramă 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D36E2CD-93E0-4E31-A161-AF4D79C440BB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Diagramă 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{558FE767-68E4-4803-A384-BEDA0D68DE1F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>38101</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>190501</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>174533</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Imagine 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E8BC3DB-F33E-9AEC-907B-41DCE498167B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8572501" y="0"/>
+          <a:ext cx="7467600" cy="3984533"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.26044</cdr:x>
+      <cdr:y>0.05229</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.79722</cdr:x>
+      <cdr:y>0.12745</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="2" name="CasetăText 1">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8D5EA3B-BDFB-C91B-8ECD-101CD1C1B1D2}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="1247776" y="152400"/>
+          <a:ext cx="2571750" cy="219075"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="square" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200"/>
+            <a:t>Diferenta de</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200" baseline="0"/>
+            <a:t> citire intre 1 grad</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200"/>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+</c:userShapes>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -371,7 +7042,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
@@ -379,9 +7050,12 @@
     <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -398,10 +7072,19 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>30</v>
       </c>
@@ -417,11 +7100,15 @@
       <c r="E2">
         <v>2725.3</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>1824.7</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I2">
+        <f>D2-G2</f>
+        <v>883.3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>31</v>
       </c>
@@ -438,10 +7125,22 @@
         <v>2687.6</v>
       </c>
       <c r="F3">
+        <f>E2-E3</f>
+        <v>37.700000000000273</v>
+      </c>
+      <c r="G3">
         <v>1781.5</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H3">
+        <f>G2-G3</f>
+        <v>43.200000000000045</v>
+      </c>
+      <c r="I3">
+        <f>D3-G3</f>
+        <v>888.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>32</v>
       </c>
@@ -458,10 +7157,22 @@
         <v>2658.4</v>
       </c>
       <c r="F4">
+        <f t="shared" ref="F4:F67" si="0">E3-E4</f>
+        <v>29.199999999999818</v>
+      </c>
+      <c r="G4">
         <v>1738.7</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H4">
+        <f t="shared" ref="H4:H67" si="1">G3-G4</f>
+        <v>42.799999999999955</v>
+      </c>
+      <c r="I4">
+        <f>D4-G4</f>
+        <v>901.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>33</v>
       </c>
@@ -478,10 +7189,22 @@
         <v>2621.7</v>
       </c>
       <c r="F5">
+        <f t="shared" si="0"/>
+        <v>36.700000000000273</v>
+      </c>
+      <c r="G5">
         <v>1696.6</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H5">
+        <f t="shared" si="1"/>
+        <v>42.100000000000136</v>
+      </c>
+      <c r="I5">
+        <f>D5-G5</f>
+        <v>908.40000000000009</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>34</v>
       </c>
@@ -498,10 +7221,22 @@
         <v>2593</v>
       </c>
       <c r="F6">
+        <f t="shared" si="0"/>
+        <v>28.699999999999818</v>
+      </c>
+      <c r="G6">
         <v>1655</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H6">
+        <f t="shared" si="1"/>
+        <v>41.599999999999909</v>
+      </c>
+      <c r="I6">
+        <f>D6-G6</f>
+        <v>920</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>35</v>
       </c>
@@ -518,10 +7253,22 @@
         <v>2558.5</v>
       </c>
       <c r="F7">
+        <f t="shared" si="0"/>
+        <v>34.5</v>
+      </c>
+      <c r="G7">
         <v>1614</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H7">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="I7">
+        <f>D7-G7</f>
+        <v>926</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>36</v>
       </c>
@@ -538,10 +7285,22 @@
         <v>2521.3000000000002</v>
       </c>
       <c r="F8">
+        <f t="shared" si="0"/>
+        <v>37.199999999999818</v>
+      </c>
+      <c r="G8">
         <v>1573.7</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H8">
+        <f t="shared" si="1"/>
+        <v>40.299999999999955</v>
+      </c>
+      <c r="I8">
+        <f>D8-G8</f>
+        <v>931.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>37</v>
       </c>
@@ -558,10 +7317,22 @@
         <v>2489.4</v>
       </c>
       <c r="F9">
+        <f t="shared" si="0"/>
+        <v>31.900000000000091</v>
+      </c>
+      <c r="G9">
         <v>1533.9</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H9">
+        <f t="shared" si="1"/>
+        <v>39.799999999999955</v>
+      </c>
+      <c r="I9">
+        <f>D9-G9</f>
+        <v>941.09999999999991</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>38</v>
       </c>
@@ -578,10 +7349,22 @@
         <v>2456.1999999999998</v>
       </c>
       <c r="F10">
+        <f t="shared" si="0"/>
+        <v>33.200000000000273</v>
+      </c>
+      <c r="G10">
         <v>1494.9</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H10">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="I10">
+        <f>D10-G10</f>
+        <v>945.09999999999991</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>39</v>
       </c>
@@ -598,10 +7381,22 @@
         <v>2422.3000000000002</v>
       </c>
       <c r="F11">
+        <f t="shared" si="0"/>
+        <v>33.899999999999636</v>
+      </c>
+      <c r="G11">
         <v>1456.5</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H11">
+        <f t="shared" si="1"/>
+        <v>38.400000000000091</v>
+      </c>
+      <c r="I11">
+        <f>D11-G11</f>
+        <v>948.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>40</v>
       </c>
@@ -618,10 +7413,22 @@
         <v>2387.8000000000002</v>
       </c>
       <c r="F12">
+        <f t="shared" si="0"/>
+        <v>34.5</v>
+      </c>
+      <c r="G12">
         <v>1418.8</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H12">
+        <f t="shared" si="1"/>
+        <v>37.700000000000045</v>
+      </c>
+      <c r="I12">
+        <f>D12-G12</f>
+        <v>956.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>41</v>
       </c>
@@ -638,10 +7445,22 @@
         <v>2362.8000000000002</v>
       </c>
       <c r="F13">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="G13">
         <v>1381.8</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H13">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="I13">
+        <f>D13-G13</f>
+        <v>968.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>42</v>
       </c>
@@ -658,10 +7477,22 @@
         <v>2329</v>
       </c>
       <c r="F14">
+        <f t="shared" si="0"/>
+        <v>33.800000000000182</v>
+      </c>
+      <c r="G14">
         <v>1345.5</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H14">
+        <f t="shared" si="1"/>
+        <v>36.299999999999955</v>
+      </c>
+      <c r="I14">
+        <f>D14-G14</f>
+        <v>969.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>43</v>
       </c>
@@ -678,10 +7509,22 @@
         <v>2284.4</v>
       </c>
       <c r="F15">
+        <f t="shared" si="0"/>
+        <v>44.599999999999909</v>
+      </c>
+      <c r="G15">
         <v>1309.9000000000001</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H15">
+        <f t="shared" si="1"/>
+        <v>35.599999999999909</v>
+      </c>
+      <c r="I15">
+        <f>D15-G15</f>
+        <v>970.09999999999991</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>44</v>
       </c>
@@ -698,10 +7541,22 @@
         <v>2253.4</v>
       </c>
       <c r="F16">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="G16">
         <v>1275.0999999999999</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H16">
+        <f t="shared" si="1"/>
+        <v>34.800000000000182</v>
+      </c>
+      <c r="I16">
+        <f>D16-G16</f>
+        <v>959.90000000000009</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>45</v>
       </c>
@@ -718,10 +7573,22 @@
         <v>2219.6999999999998</v>
       </c>
       <c r="F17">
+        <f t="shared" si="0"/>
+        <v>33.700000000000273</v>
+      </c>
+      <c r="G17">
         <v>1241</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H17">
+        <f t="shared" si="1"/>
+        <v>34.099999999999909</v>
+      </c>
+      <c r="I17">
+        <f>D17-G17</f>
+        <v>964</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>46</v>
       </c>
@@ -738,10 +7605,22 @@
         <v>2185.1999999999998</v>
       </c>
       <c r="F18">
+        <f t="shared" si="0"/>
+        <v>34.5</v>
+      </c>
+      <c r="G18">
         <v>1207.5999999999999</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H18">
+        <f t="shared" si="1"/>
+        <v>33.400000000000091</v>
+      </c>
+      <c r="I18">
+        <f>D18-G18</f>
+        <v>962.40000000000009</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>47</v>
       </c>
@@ -758,10 +7637,22 @@
         <v>2154.3000000000002</v>
       </c>
       <c r="F19">
+        <f t="shared" si="0"/>
+        <v>30.899999999999636</v>
+      </c>
+      <c r="G19">
         <v>1174.9000000000001</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H19">
+        <f t="shared" si="1"/>
+        <v>32.699999999999818</v>
+      </c>
+      <c r="I19">
+        <f>D19-G19</f>
+        <v>965.09999999999991</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>48</v>
       </c>
@@ -778,10 +7669,22 @@
         <v>2128.1999999999998</v>
       </c>
       <c r="F20">
+        <f t="shared" si="0"/>
+        <v>26.100000000000364</v>
+      </c>
+      <c r="G20">
         <v>1143</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H20">
+        <f t="shared" si="1"/>
+        <v>31.900000000000091</v>
+      </c>
+      <c r="I20">
+        <f>D20-G20</f>
+        <v>972</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>49</v>
       </c>
@@ -798,10 +7701,22 @@
         <v>2097.6</v>
       </c>
       <c r="F21">
+        <f t="shared" si="0"/>
+        <v>30.599999999999909</v>
+      </c>
+      <c r="G21">
         <v>1111.8</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H21">
+        <f t="shared" si="1"/>
+        <v>31.200000000000045</v>
+      </c>
+      <c r="I21">
+        <f>D21-G21</f>
+        <v>973.2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>50</v>
       </c>
@@ -818,10 +7733,22 @@
         <v>2058.6</v>
       </c>
       <c r="F22">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="G22">
         <v>1081.4000000000001</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H22">
+        <f t="shared" si="1"/>
+        <v>30.399999999999864</v>
+      </c>
+      <c r="I22">
+        <f>D22-G22</f>
+        <v>963.59999999999991</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>51</v>
       </c>
@@ -838,10 +7765,22 @@
         <v>2028.2</v>
       </c>
       <c r="F23">
+        <f t="shared" si="0"/>
+        <v>30.399999999999864</v>
+      </c>
+      <c r="G23">
         <v>1051.5999999999999</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H23">
+        <f t="shared" si="1"/>
+        <v>29.800000000000182</v>
+      </c>
+      <c r="I23">
+        <f>D23-G23</f>
+        <v>963.40000000000009</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>52</v>
       </c>
@@ -858,10 +7797,22 @@
         <v>1998.5</v>
       </c>
       <c r="F24">
+        <f t="shared" si="0"/>
+        <v>29.700000000000045</v>
+      </c>
+      <c r="G24">
         <v>1022.6</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H24">
+        <f t="shared" si="1"/>
+        <v>28.999999999999886</v>
+      </c>
+      <c r="I24">
+        <f>D24-G24</f>
+        <v>962.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>53</v>
       </c>
@@ -878,10 +7829,22 @@
         <v>1967.6</v>
       </c>
       <c r="F25">
+        <f t="shared" si="0"/>
+        <v>30.900000000000091</v>
+      </c>
+      <c r="G25">
         <v>994.28</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H25">
+        <f t="shared" si="1"/>
+        <v>28.32000000000005</v>
+      </c>
+      <c r="I25">
+        <f>D25-G25</f>
+        <v>960.72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>54</v>
       </c>
@@ -898,10 +7861,22 @@
         <v>1938.7</v>
       </c>
       <c r="F26">
+        <f t="shared" si="0"/>
+        <v>28.899999999999864</v>
+      </c>
+      <c r="G26">
         <v>966.67</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H26">
+        <f t="shared" si="1"/>
+        <v>27.610000000000014</v>
+      </c>
+      <c r="I26">
+        <f>D26-G26</f>
+        <v>963.33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>55</v>
       </c>
@@ -918,10 +7893,22 @@
         <v>1909.9</v>
       </c>
       <c r="F27">
+        <f t="shared" si="0"/>
+        <v>28.799999999999955</v>
+      </c>
+      <c r="G27">
         <v>939.77</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H27">
+        <f t="shared" si="1"/>
+        <v>26.899999999999977</v>
+      </c>
+      <c r="I27">
+        <f>D27-G27</f>
+        <v>960.23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>56</v>
       </c>
@@ -938,10 +7925,22 @@
         <v>1884.2</v>
       </c>
       <c r="F28">
+        <f t="shared" si="0"/>
+        <v>25.700000000000045</v>
+      </c>
+      <c r="G28">
         <v>913.55</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H28">
+        <f t="shared" si="1"/>
+        <v>26.220000000000027</v>
+      </c>
+      <c r="I28">
+        <f>D28-G28</f>
+        <v>961.45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>57</v>
       </c>
@@ -958,10 +7957,22 @@
         <v>1854.7</v>
       </c>
       <c r="F29">
+        <f t="shared" si="0"/>
+        <v>29.5</v>
+      </c>
+      <c r="G29">
         <v>888.01</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H29">
+        <f t="shared" si="1"/>
+        <v>25.539999999999964</v>
+      </c>
+      <c r="I29">
+        <f>D29-G29</f>
+        <v>956.99</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>58</v>
       </c>
@@ -978,10 +7989,22 @@
         <v>1826.4</v>
       </c>
       <c r="F30">
+        <f t="shared" si="0"/>
+        <v>28.299999999999955</v>
+      </c>
+      <c r="G30">
         <v>863.14</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H30">
+        <f t="shared" si="1"/>
+        <v>24.870000000000005</v>
+      </c>
+      <c r="I30">
+        <f>D30-G30</f>
+        <v>951.86</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>59</v>
       </c>
@@ -998,10 +8021,22 @@
         <v>1798.6</v>
       </c>
       <c r="F31">
+        <f t="shared" si="0"/>
+        <v>27.800000000000182</v>
+      </c>
+      <c r="G31">
         <v>838.93</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H31">
+        <f t="shared" si="1"/>
+        <v>24.210000000000036</v>
+      </c>
+      <c r="I31">
+        <f>D31-G31</f>
+        <v>951.07</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>60</v>
       </c>
@@ -1018,10 +8053,22 @@
         <v>1771.3</v>
       </c>
       <c r="F32">
+        <f t="shared" si="0"/>
+        <v>27.299999999999955</v>
+      </c>
+      <c r="G32">
         <v>815.37</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H32">
+        <f t="shared" si="1"/>
+        <v>23.559999999999945</v>
+      </c>
+      <c r="I32">
+        <f>D32-G32</f>
+        <v>944.63</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>61</v>
       </c>
@@ -1038,10 +8085,22 @@
         <v>1744.6</v>
       </c>
       <c r="F33">
+        <f t="shared" si="0"/>
+        <v>26.700000000000045</v>
+      </c>
+      <c r="G33">
         <v>792.45</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H33">
+        <f t="shared" si="1"/>
+        <v>22.919999999999959</v>
+      </c>
+      <c r="I33">
+        <f>D33-G33</f>
+        <v>942.55</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>62</v>
       </c>
@@ -1058,10 +8117,22 @@
         <v>1714.9</v>
       </c>
       <c r="F34">
+        <f t="shared" si="0"/>
+        <v>29.699999999999818</v>
+      </c>
+      <c r="G34">
         <v>770.15</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H34">
+        <f t="shared" si="1"/>
+        <v>22.300000000000068</v>
+      </c>
+      <c r="I34">
+        <f>D34-G34</f>
+        <v>934.85</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>63</v>
       </c>
@@ -1078,10 +8149,22 @@
         <v>1689.1</v>
       </c>
       <c r="F35">
+        <f t="shared" si="0"/>
+        <v>25.800000000000182</v>
+      </c>
+      <c r="G35">
         <v>748.46</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H35">
+        <f t="shared" si="1"/>
+        <v>21.689999999999941</v>
+      </c>
+      <c r="I35">
+        <f>D35-G35</f>
+        <v>931.54</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>64</v>
       </c>
@@ -1098,10 +8181,22 @@
         <v>1661.8</v>
       </c>
       <c r="F36">
+        <f t="shared" si="0"/>
+        <v>27.299999999999955</v>
+      </c>
+      <c r="G36">
         <v>727.38</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H36">
+        <f t="shared" si="1"/>
+        <v>21.080000000000041</v>
+      </c>
+      <c r="I36">
+        <f>D36-G36</f>
+        <v>927.62</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>65</v>
       </c>
@@ -1118,10 +8213,22 @@
         <v>1637.4</v>
       </c>
       <c r="F37">
+        <f t="shared" si="0"/>
+        <v>24.399999999999864</v>
+      </c>
+      <c r="G37">
         <v>706.89</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H37">
+        <f t="shared" si="1"/>
+        <v>20.490000000000009</v>
+      </c>
+      <c r="I37">
+        <f>D37-G37</f>
+        <v>923.11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>66</v>
       </c>
@@ -1138,10 +8245,22 @@
         <v>1611.2</v>
       </c>
       <c r="F38">
+        <f t="shared" si="0"/>
+        <v>26.200000000000045</v>
+      </c>
+      <c r="G38">
         <v>686.97</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H38">
+        <f t="shared" si="1"/>
+        <v>19.919999999999959</v>
+      </c>
+      <c r="I38">
+        <f>D38-G38</f>
+        <v>920.03</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>67</v>
       </c>
@@ -1158,10 +8277,22 @@
         <v>1587.3</v>
       </c>
       <c r="F39">
+        <f t="shared" si="0"/>
+        <v>23.900000000000091</v>
+      </c>
+      <c r="G39">
         <v>667.62</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H39">
+        <f t="shared" si="1"/>
+        <v>19.350000000000023</v>
+      </c>
+      <c r="I39">
+        <f>D39-G39</f>
+        <v>912.38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>68</v>
       </c>
@@ -1178,10 +8309,22 @@
         <v>1566.2</v>
       </c>
       <c r="F40">
+        <f t="shared" si="0"/>
+        <v>21.099999999999909</v>
+      </c>
+      <c r="G40">
         <v>648.80999999999995</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H40">
+        <f t="shared" si="1"/>
+        <v>18.810000000000059</v>
+      </c>
+      <c r="I40">
+        <f>D40-G40</f>
+        <v>909.19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>69</v>
       </c>
@@ -1198,10 +8341,22 @@
         <v>1532.8</v>
       </c>
       <c r="F41">
+        <f t="shared" si="0"/>
+        <v>33.400000000000091</v>
+      </c>
+      <c r="G41">
         <v>630.54999999999995</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H41">
+        <f t="shared" si="1"/>
+        <v>18.259999999999991</v>
+      </c>
+      <c r="I41">
+        <f>D41-G41</f>
+        <v>902.45</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>70</v>
       </c>
@@ -1218,10 +8373,22 @@
         <v>1510.7</v>
       </c>
       <c r="F42">
+        <f t="shared" si="0"/>
+        <v>22.099999999999909</v>
+      </c>
+      <c r="G42">
         <v>612.80999999999995</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H42">
+        <f t="shared" si="1"/>
+        <v>17.740000000000009</v>
+      </c>
+      <c r="I42">
+        <f>D42-G42</f>
+        <v>873.19</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>71</v>
       </c>
@@ -1238,10 +8405,22 @@
         <v>1459.9</v>
       </c>
       <c r="F43">
+        <f t="shared" si="0"/>
+        <v>50.799999999999955</v>
+      </c>
+      <c r="G43">
         <v>595.58000000000004</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H43">
+        <f t="shared" si="1"/>
+        <v>17.229999999999905</v>
+      </c>
+      <c r="I43">
+        <f>D43-G43</f>
+        <v>867.42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>72</v>
       </c>
@@ -1258,10 +8437,22 @@
         <v>1432.8</v>
       </c>
       <c r="F44">
+        <f t="shared" si="0"/>
+        <v>27.100000000000136</v>
+      </c>
+      <c r="G44">
         <v>578.86</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H44">
+        <f t="shared" si="1"/>
+        <v>16.720000000000027</v>
+      </c>
+      <c r="I44">
+        <f>D44-G44</f>
+        <v>840.14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>73</v>
       </c>
@@ -1278,10 +8469,22 @@
         <v>1401.1</v>
       </c>
       <c r="F45">
+        <f t="shared" si="0"/>
+        <v>31.700000000000045</v>
+      </c>
+      <c r="G45">
         <v>562.62</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H45">
+        <f t="shared" si="1"/>
+        <v>16.240000000000009</v>
+      </c>
+      <c r="I45">
+        <f>D45-G45</f>
+        <v>819.38</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>74</v>
       </c>
@@ -1298,10 +8501,22 @@
         <v>1386.2</v>
       </c>
       <c r="F46">
+        <f t="shared" si="0"/>
+        <v>14.899999999999864</v>
+      </c>
+      <c r="G46">
         <v>546.85</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H46">
+        <f t="shared" si="1"/>
+        <v>15.769999999999982</v>
+      </c>
+      <c r="I46">
+        <f>D46-G46</f>
+        <v>757.15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>75</v>
       </c>
@@ -1318,10 +8533,22 @@
         <v>1317.8</v>
       </c>
       <c r="F47">
+        <f t="shared" si="0"/>
+        <v>68.400000000000091</v>
+      </c>
+      <c r="G47">
         <v>531.54999999999995</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H47">
+        <f t="shared" si="1"/>
+        <v>15.300000000000068</v>
+      </c>
+      <c r="I47">
+        <f>D47-G47</f>
+        <v>833.45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>76</v>
       </c>
@@ -1338,10 +8565,22 @@
         <v>1279.5999999999999</v>
       </c>
       <c r="F48">
+        <f t="shared" si="0"/>
+        <v>38.200000000000045</v>
+      </c>
+      <c r="G48">
         <v>516.70000000000005</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H48">
+        <f t="shared" si="1"/>
+        <v>14.849999999999909</v>
+      </c>
+      <c r="I48">
+        <f>D48-G48</f>
+        <v>753.3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>77</v>
       </c>
@@ -1358,10 +8597,22 @@
         <v>1255.2</v>
       </c>
       <c r="F49">
+        <f t="shared" si="0"/>
+        <v>24.399999999999864</v>
+      </c>
+      <c r="G49">
         <v>502.29</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H49">
+        <f t="shared" si="1"/>
+        <v>14.410000000000025</v>
+      </c>
+      <c r="I49">
+        <f>D49-G49</f>
+        <v>752.71</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>78</v>
       </c>
@@ -1378,10 +8629,22 @@
         <v>1226.5999999999999</v>
       </c>
       <c r="F50">
+        <f t="shared" si="0"/>
+        <v>28.600000000000136</v>
+      </c>
+      <c r="G50">
         <v>488.3</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H50">
+        <f t="shared" si="1"/>
+        <v>13.990000000000009</v>
+      </c>
+      <c r="I50">
+        <f>D50-G50</f>
+        <v>738.7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>79</v>
       </c>
@@ -1398,10 +8661,22 @@
         <v>1177.4000000000001</v>
       </c>
       <c r="F51">
+        <f t="shared" si="0"/>
+        <v>49.199999999999818</v>
+      </c>
+      <c r="G51">
         <v>474.73</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H51">
+        <f t="shared" si="1"/>
+        <v>13.569999999999993</v>
+      </c>
+      <c r="I51">
+        <f>D51-G51</f>
+        <v>699.27</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>80</v>
       </c>
@@ -1418,10 +8693,22 @@
         <v>1161.2</v>
       </c>
       <c r="F52">
+        <f t="shared" si="0"/>
+        <v>16.200000000000045</v>
+      </c>
+      <c r="G52">
         <v>461.56</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H52">
+        <f t="shared" si="1"/>
+        <v>13.170000000000016</v>
+      </c>
+      <c r="I52">
+        <f>D52-G52</f>
+        <v>696.44</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>81</v>
       </c>
@@ -1438,10 +8725,22 @@
         <v>1134.9000000000001</v>
       </c>
       <c r="F53">
+        <f t="shared" si="0"/>
+        <v>26.299999999999955</v>
+      </c>
+      <c r="G53">
         <v>448.79</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H53">
+        <f t="shared" si="1"/>
+        <v>12.769999999999982</v>
+      </c>
+      <c r="I53">
+        <f>D53-G53</f>
+        <v>684.21</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>82</v>
       </c>
@@ -1458,10 +8757,22 @@
         <v>1121.7</v>
       </c>
       <c r="F54">
+        <f t="shared" si="0"/>
+        <v>13.200000000000045</v>
+      </c>
+      <c r="G54">
         <v>436.39</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H54">
+        <f t="shared" si="1"/>
+        <v>12.400000000000034</v>
+      </c>
+      <c r="I54">
+        <f>D54-G54</f>
+        <v>682.61</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>83</v>
       </c>
@@ -1478,10 +8789,22 @@
         <v>1108.5</v>
       </c>
       <c r="F55">
+        <f t="shared" si="0"/>
+        <v>13.200000000000045</v>
+      </c>
+      <c r="G55">
         <v>424.36</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H55">
+        <f t="shared" si="1"/>
+        <v>12.029999999999973</v>
+      </c>
+      <c r="I55">
+        <f>D55-G55</f>
+        <v>681.64</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>84</v>
       </c>
@@ -1498,10 +8821,22 @@
         <v>1097.5999999999999</v>
       </c>
       <c r="F56">
+        <f t="shared" si="0"/>
+        <v>10.900000000000091</v>
+      </c>
+      <c r="G56">
         <v>412.69</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H56">
+        <f t="shared" si="1"/>
+        <v>11.670000000000016</v>
+      </c>
+      <c r="I56">
+        <f>D56-G56</f>
+        <v>682.31</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>85</v>
       </c>
@@ -1518,10 +8853,22 @@
         <v>1083.8</v>
       </c>
       <c r="F57">
+        <f t="shared" si="0"/>
+        <v>13.799999999999955</v>
+      </c>
+      <c r="G57">
         <v>401.38</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H57">
+        <f t="shared" si="1"/>
+        <v>11.310000000000002</v>
+      </c>
+      <c r="I57">
+        <f>D57-G57</f>
+        <v>680.62</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>86</v>
       </c>
@@ -1538,10 +8885,22 @@
         <v>1074.9000000000001</v>
       </c>
       <c r="F58">
+        <f t="shared" si="0"/>
+        <v>8.8999999999998636</v>
+      </c>
+      <c r="G58">
         <v>390.39</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H58">
+        <f t="shared" si="1"/>
+        <v>10.990000000000009</v>
+      </c>
+      <c r="I58">
+        <f>D58-G58</f>
+        <v>681.61</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>87</v>
       </c>
@@ -1558,10 +8917,22 @@
         <v>1063.3</v>
       </c>
       <c r="F59">
+        <f t="shared" si="0"/>
+        <v>11.600000000000136</v>
+      </c>
+      <c r="G59">
         <v>379.74</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H59">
+        <f t="shared" si="1"/>
+        <v>10.649999999999977</v>
+      </c>
+      <c r="I59">
+        <f>D59-G59</f>
+        <v>681.26</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>88</v>
       </c>
@@ -1578,10 +8949,22 @@
         <v>1052.2</v>
       </c>
       <c r="F60">
+        <f t="shared" si="0"/>
+        <v>11.099999999999909</v>
+      </c>
+      <c r="G60">
         <v>369.41</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H60">
+        <f t="shared" si="1"/>
+        <v>10.329999999999984</v>
+      </c>
+      <c r="I60">
+        <f>D60-G60</f>
+        <v>680.58999999999992</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>89</v>
       </c>
@@ -1598,10 +8981,22 @@
         <v>1040.2</v>
       </c>
       <c r="F61">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="G61">
         <v>359.38</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H61">
+        <f t="shared" si="1"/>
+        <v>10.03000000000003</v>
+      </c>
+      <c r="I61">
+        <f>D61-G61</f>
+        <v>677.62</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>90</v>
       </c>
@@ -1618,10 +9013,22 @@
         <v>1025.3</v>
       </c>
       <c r="F62">
+        <f t="shared" si="0"/>
+        <v>14.900000000000091</v>
+      </c>
+      <c r="G62">
         <v>349.66</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H62">
+        <f t="shared" si="1"/>
+        <v>9.7199999999999704</v>
+      </c>
+      <c r="I62">
+        <f>D62-G62</f>
+        <v>673.33999999999992</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>91</v>
       </c>
@@ -1638,10 +9045,22 @@
         <v>1016.1</v>
       </c>
       <c r="F63">
+        <f t="shared" si="0"/>
+        <v>9.1999999999999318</v>
+      </c>
+      <c r="G63">
         <v>340.22</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H63">
+        <f t="shared" si="1"/>
+        <v>9.4399999999999977</v>
+      </c>
+      <c r="I63">
+        <f>D63-G63</f>
+        <v>673.78</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>92</v>
       </c>
@@ -1658,10 +9077,22 @@
         <v>1005.8</v>
       </c>
       <c r="F64">
+        <f t="shared" si="0"/>
+        <v>10.300000000000068</v>
+      </c>
+      <c r="G64">
         <v>331.07</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H64">
+        <f t="shared" si="1"/>
+        <v>9.1500000000000341</v>
+      </c>
+      <c r="I64">
+        <f>D64-G64</f>
+        <v>670.93000000000006</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>93</v>
       </c>
@@ -1678,10 +9109,22 @@
         <v>995.61</v>
       </c>
       <c r="F65">
+        <f t="shared" si="0"/>
+        <v>10.189999999999941</v>
+      </c>
+      <c r="G65">
         <v>322.19</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H65">
+        <f t="shared" si="1"/>
+        <v>8.8799999999999955</v>
+      </c>
+      <c r="I65">
+        <f>D65-G65</f>
+        <v>669.81</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>94</v>
       </c>
@@ -1698,10 +9141,22 @@
         <v>983.24</v>
       </c>
       <c r="F66">
+        <f t="shared" si="0"/>
+        <v>12.370000000000005</v>
+      </c>
+      <c r="G66">
         <v>313.57</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H66">
+        <f t="shared" si="1"/>
+        <v>8.6200000000000045</v>
+      </c>
+      <c r="I66">
+        <f>D66-G66</f>
+        <v>667.43000000000006</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>95</v>
       </c>
@@ -1718,10 +9173,22 @@
         <v>972.46</v>
       </c>
       <c r="F67">
+        <f t="shared" si="0"/>
+        <v>10.779999999999973</v>
+      </c>
+      <c r="G67">
         <v>305.22000000000003</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H67">
+        <f t="shared" si="1"/>
+        <v>8.3499999999999659</v>
+      </c>
+      <c r="I67">
+        <f>D67-G67</f>
+        <v>664.78</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>96</v>
       </c>
@@ -1738,10 +9205,22 @@
         <v>963.86</v>
       </c>
       <c r="F68">
+        <f t="shared" ref="F68:F83" si="2">E67-E68</f>
+        <v>8.6000000000000227</v>
+      </c>
+      <c r="G68">
         <v>297.11</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H68">
+        <f t="shared" ref="H68:H82" si="3">G67-G68</f>
+        <v>8.1100000000000136</v>
+      </c>
+      <c r="I68">
+        <f>D68-G68</f>
+        <v>662.89</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>97</v>
       </c>
@@ -1758,10 +9237,22 @@
         <v>953.79</v>
       </c>
       <c r="F69">
+        <f t="shared" si="2"/>
+        <v>10.07000000000005</v>
+      </c>
+      <c r="G69">
         <v>289.24</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H69">
+        <f t="shared" si="3"/>
+        <v>7.8700000000000045</v>
+      </c>
+      <c r="I69">
+        <f>D69-G69</f>
+        <v>660.76</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>98</v>
       </c>
@@ -1778,10 +9269,22 @@
         <v>943.54</v>
       </c>
       <c r="F70">
+        <f t="shared" si="2"/>
+        <v>10.25</v>
+      </c>
+      <c r="G70">
         <v>281.61</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H70">
+        <f t="shared" si="3"/>
+        <v>7.6299999999999955</v>
+      </c>
+      <c r="I70">
+        <f>D70-G70</f>
+        <v>659.39</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>99</v>
       </c>
@@ -1798,10 +9301,22 @@
         <v>932.31</v>
       </c>
       <c r="F71">
+        <f t="shared" si="2"/>
+        <v>11.230000000000018</v>
+      </c>
+      <c r="G71">
         <v>274.2</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H71">
+        <f t="shared" si="3"/>
+        <v>7.410000000000025</v>
+      </c>
+      <c r="I71">
+        <f>D71-G71</f>
+        <v>654.79999999999995</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>100</v>
       </c>
@@ -1818,10 +9333,22 @@
         <v>922.86</v>
       </c>
       <c r="F72">
+        <f t="shared" si="2"/>
+        <v>9.4499999999999318</v>
+      </c>
+      <c r="G72">
         <v>267.01</v>
       </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H72">
+        <f t="shared" si="3"/>
+        <v>7.1899999999999977</v>
+      </c>
+      <c r="I72">
+        <f>D72-G72</f>
+        <v>652.99</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>101</v>
       </c>
@@ -1838,10 +9365,22 @@
         <v>913.54</v>
       </c>
       <c r="F73">
+        <f t="shared" si="2"/>
+        <v>9.32000000000005</v>
+      </c>
+      <c r="G73">
         <v>260.02999999999997</v>
       </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H73">
+        <f t="shared" si="3"/>
+        <v>6.9800000000000182</v>
+      </c>
+      <c r="I73">
+        <f>D73-G73</f>
+        <v>650.97</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>102</v>
       </c>
@@ -1858,10 +9397,22 @@
         <v>902.67</v>
       </c>
       <c r="F74">
+        <f t="shared" si="2"/>
+        <v>10.870000000000005</v>
+      </c>
+      <c r="G74">
         <v>253.26</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H74">
+        <f t="shared" si="3"/>
+        <v>6.7699999999999818</v>
+      </c>
+      <c r="I74">
+        <f>D74-G74</f>
+        <v>646.74</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>103</v>
       </c>
@@ -1878,10 +9429,22 @@
         <v>894.42</v>
       </c>
       <c r="F75">
+        <f t="shared" si="2"/>
+        <v>8.25</v>
+      </c>
+      <c r="G75">
         <v>246.7</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H75">
+        <f t="shared" si="3"/>
+        <v>6.5600000000000023</v>
+      </c>
+      <c r="I75">
+        <f>D75-G75</f>
+        <v>644.29999999999995</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>104</v>
       </c>
@@ -1898,10 +9461,22 @@
         <v>886.29</v>
       </c>
       <c r="F76">
+        <f t="shared" si="2"/>
+        <v>8.1299999999999955</v>
+      </c>
+      <c r="G76">
         <v>240.32</v>
       </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H76">
+        <f t="shared" si="3"/>
+        <v>6.3799999999999955</v>
+      </c>
+      <c r="I76">
+        <f>D76-G76</f>
+        <v>642.68000000000006</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>105</v>
       </c>
@@ -1918,10 +9493,22 @@
         <v>876.4</v>
       </c>
       <c r="F77">
+        <f t="shared" si="2"/>
+        <v>9.8899999999999864</v>
+      </c>
+      <c r="G77">
         <v>234.13</v>
       </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H77">
+        <f t="shared" si="3"/>
+        <v>6.1899999999999977</v>
+      </c>
+      <c r="I77">
+        <f>D77-G77</f>
+        <v>638.87</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>106</v>
       </c>
@@ -1938,10 +9525,22 @@
         <v>867.89</v>
       </c>
       <c r="F78">
+        <f t="shared" si="2"/>
+        <v>8.5099999999999909</v>
+      </c>
+      <c r="G78">
         <v>228.12</v>
       </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H78">
+        <f t="shared" si="3"/>
+        <v>6.0099999999999909</v>
+      </c>
+      <c r="I78">
+        <f>D78-G78</f>
+        <v>635.88</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>107</v>
       </c>
@@ -1958,10 +9557,22 @@
         <v>859.74</v>
       </c>
       <c r="F79">
+        <f t="shared" si="2"/>
+        <v>8.1499999999999773</v>
+      </c>
+      <c r="G79">
         <v>222.29</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H79">
+        <f t="shared" si="3"/>
+        <v>5.8300000000000125</v>
+      </c>
+      <c r="I79">
+        <f>D79-G79</f>
+        <v>633.71</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>108</v>
       </c>
@@ -1978,10 +9589,22 @@
         <v>852</v>
       </c>
       <c r="F80">
+        <f t="shared" si="2"/>
+        <v>7.7400000000000091</v>
+      </c>
+      <c r="G80">
         <v>216.63</v>
       </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H80">
+        <f t="shared" si="3"/>
+        <v>5.6599999999999966</v>
+      </c>
+      <c r="I80">
+        <f>D80-G80</f>
+        <v>632.37</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>109</v>
       </c>
@@ -1998,10 +9621,22 @@
         <v>843.72</v>
       </c>
       <c r="F81">
+        <f t="shared" si="2"/>
+        <v>8.2799999999999727</v>
+      </c>
+      <c r="G81">
         <v>211.13</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H81">
+        <f t="shared" si="3"/>
+        <v>5.5</v>
+      </c>
+      <c r="I81">
+        <f>D81-G81</f>
+        <v>629.87</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>110</v>
       </c>
@@ -2018,11 +9653,1052 @@
         <v>836.18</v>
       </c>
       <c r="F82">
+        <f t="shared" si="2"/>
+        <v>7.5400000000000773</v>
+      </c>
+      <c r="G82">
         <v>205.79</v>
+      </c>
+      <c r="H82">
+        <f t="shared" si="3"/>
+        <v>5.3400000000000034</v>
+      </c>
+      <c r="I82">
+        <f>D82-G82</f>
+        <v>627.21</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{029070C6-C74E-46B2-ACE6-E48FDF41C159}">
+  <dimension ref="B1:D152"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B22">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B28">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B29">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B30">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B31">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B32">
+        <v>30</v>
+      </c>
+      <c r="C32">
+        <v>2725.3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B33">
+        <v>31</v>
+      </c>
+      <c r="C33">
+        <v>2687.6</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B34">
+        <v>32</v>
+      </c>
+      <c r="C34">
+        <v>2658.4</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B35">
+        <v>33</v>
+      </c>
+      <c r="C35">
+        <v>2621.7</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B36">
+        <v>34</v>
+      </c>
+      <c r="C36">
+        <v>2593</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B37">
+        <v>35</v>
+      </c>
+      <c r="C37">
+        <v>2558.5</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B38">
+        <v>36</v>
+      </c>
+      <c r="C38">
+        <v>2521.3000000000002</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B39">
+        <v>37</v>
+      </c>
+      <c r="C39">
+        <v>2489.4</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B40">
+        <v>38</v>
+      </c>
+      <c r="C40">
+        <v>2456.1999999999998</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B41">
+        <v>39</v>
+      </c>
+      <c r="C41">
+        <v>2422.3000000000002</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B42">
+        <v>40</v>
+      </c>
+      <c r="C42">
+        <v>2387.8000000000002</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B43">
+        <v>41</v>
+      </c>
+      <c r="C43">
+        <v>2362.8000000000002</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B44">
+        <v>42</v>
+      </c>
+      <c r="C44">
+        <v>2329</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B45">
+        <v>43</v>
+      </c>
+      <c r="C45">
+        <v>2284.4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B46">
+        <v>44</v>
+      </c>
+      <c r="C46">
+        <v>2253.4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B47">
+        <v>45</v>
+      </c>
+      <c r="C47">
+        <v>2219.6999999999998</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B48">
+        <v>46</v>
+      </c>
+      <c r="C48">
+        <v>2185.1999999999998</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B49">
+        <v>47</v>
+      </c>
+      <c r="C49">
+        <v>2154.3000000000002</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B50">
+        <v>48</v>
+      </c>
+      <c r="C50">
+        <v>2128.1999999999998</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B51">
+        <v>49</v>
+      </c>
+      <c r="C51">
+        <v>2097.6</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B52">
+        <v>50</v>
+      </c>
+      <c r="C52">
+        <v>2058.6</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B53">
+        <v>51</v>
+      </c>
+      <c r="C53">
+        <v>2028.2</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B54">
+        <v>52</v>
+      </c>
+      <c r="C54">
+        <v>1998.5</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B55">
+        <v>53</v>
+      </c>
+      <c r="C55">
+        <v>1967.6</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B56">
+        <v>54</v>
+      </c>
+      <c r="C56">
+        <v>1938.7</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B57">
+        <v>55</v>
+      </c>
+      <c r="C57">
+        <v>1909.9</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B58">
+        <v>56</v>
+      </c>
+      <c r="C58">
+        <v>1884.2</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B59">
+        <v>57</v>
+      </c>
+      <c r="C59">
+        <v>1854.7</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B60">
+        <v>58</v>
+      </c>
+      <c r="C60">
+        <v>1826.4</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B61">
+        <v>59</v>
+      </c>
+      <c r="C61">
+        <v>1798.6</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B62">
+        <v>60</v>
+      </c>
+      <c r="C62">
+        <v>1771.3</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B63">
+        <v>61</v>
+      </c>
+      <c r="C63">
+        <v>1744.6</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B64">
+        <v>62</v>
+      </c>
+      <c r="C64">
+        <v>1714.9</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B65">
+        <v>63</v>
+      </c>
+      <c r="C65">
+        <v>1689.1</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B66">
+        <v>64</v>
+      </c>
+      <c r="C66">
+        <v>1661.8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B67">
+        <v>65</v>
+      </c>
+      <c r="C67">
+        <v>1637.4</v>
+      </c>
+    </row>
+    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B68">
+        <v>66</v>
+      </c>
+      <c r="C68">
+        <v>1611.2</v>
+      </c>
+    </row>
+    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B69">
+        <v>67</v>
+      </c>
+      <c r="C69">
+        <v>1587.3</v>
+      </c>
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B70">
+        <v>68</v>
+      </c>
+      <c r="C70">
+        <v>1566.2</v>
+      </c>
+    </row>
+    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B71">
+        <v>69</v>
+      </c>
+      <c r="C71">
+        <v>1532.8</v>
+      </c>
+    </row>
+    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B72">
+        <v>70</v>
+      </c>
+      <c r="C72">
+        <v>1510.7</v>
+      </c>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B73">
+        <v>71</v>
+      </c>
+      <c r="C73">
+        <v>1459.9</v>
+      </c>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B74">
+        <v>72</v>
+      </c>
+      <c r="C74">
+        <v>1432.8</v>
+      </c>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B75">
+        <v>73</v>
+      </c>
+      <c r="C75">
+        <v>1401.1</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B76">
+        <v>74</v>
+      </c>
+      <c r="C76">
+        <v>1386.2</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B77">
+        <v>75</v>
+      </c>
+      <c r="C77">
+        <v>1317.8</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B78">
+        <v>76</v>
+      </c>
+      <c r="C78">
+        <v>1279.5999999999999</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B79">
+        <v>77</v>
+      </c>
+      <c r="C79">
+        <v>1255.2</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B80">
+        <v>78</v>
+      </c>
+      <c r="C80">
+        <v>1226.5999999999999</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B81">
+        <v>79</v>
+      </c>
+      <c r="C81">
+        <v>1177.4000000000001</v>
+      </c>
+      <c r="D81" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B82">
+        <v>80</v>
+      </c>
+      <c r="C82">
+        <v>1161.2</v>
+      </c>
+    </row>
+    <row r="83" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B83">
+        <v>81</v>
+      </c>
+      <c r="C83">
+        <v>1134.9000000000001</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B84">
+        <v>82</v>
+      </c>
+      <c r="C84">
+        <v>1121.7</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B85">
+        <v>83</v>
+      </c>
+      <c r="C85">
+        <v>1108.5</v>
+      </c>
+    </row>
+    <row r="86" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B86">
+        <v>84</v>
+      </c>
+      <c r="C86">
+        <v>1097.5999999999999</v>
+      </c>
+    </row>
+    <row r="87" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B87">
+        <v>85</v>
+      </c>
+      <c r="C87">
+        <v>1083.8</v>
+      </c>
+    </row>
+    <row r="88" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B88">
+        <v>86</v>
+      </c>
+      <c r="C88">
+        <v>1074.9000000000001</v>
+      </c>
+    </row>
+    <row r="89" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B89">
+        <v>87</v>
+      </c>
+      <c r="C89">
+        <v>1063.3</v>
+      </c>
+    </row>
+    <row r="90" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B90">
+        <v>88</v>
+      </c>
+      <c r="C90">
+        <v>1052.2</v>
+      </c>
+    </row>
+    <row r="91" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B91">
+        <v>89</v>
+      </c>
+      <c r="C91">
+        <v>1040.2</v>
+      </c>
+    </row>
+    <row r="92" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B92">
+        <v>90</v>
+      </c>
+      <c r="C92">
+        <v>1025.3</v>
+      </c>
+    </row>
+    <row r="93" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B93">
+        <v>91</v>
+      </c>
+      <c r="C93">
+        <v>1016.1</v>
+      </c>
+    </row>
+    <row r="94" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B94">
+        <v>92</v>
+      </c>
+      <c r="C94">
+        <v>1005.8</v>
+      </c>
+    </row>
+    <row r="95" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B95">
+        <v>93</v>
+      </c>
+      <c r="C95">
+        <v>995.61</v>
+      </c>
+    </row>
+    <row r="96" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B96">
+        <v>94</v>
+      </c>
+      <c r="C96">
+        <v>983.24</v>
+      </c>
+    </row>
+    <row r="97" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B97">
+        <v>95</v>
+      </c>
+      <c r="C97">
+        <v>972.46</v>
+      </c>
+    </row>
+    <row r="98" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B98">
+        <v>96</v>
+      </c>
+      <c r="C98">
+        <v>963.86</v>
+      </c>
+    </row>
+    <row r="99" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B99">
+        <v>97</v>
+      </c>
+      <c r="C99">
+        <v>953.79</v>
+      </c>
+    </row>
+    <row r="100" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B100">
+        <v>98</v>
+      </c>
+      <c r="C100">
+        <v>943.54</v>
+      </c>
+    </row>
+    <row r="101" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B101">
+        <v>99</v>
+      </c>
+      <c r="C101">
+        <v>932.31</v>
+      </c>
+    </row>
+    <row r="102" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B102">
+        <v>100</v>
+      </c>
+      <c r="C102">
+        <v>922.86</v>
+      </c>
+    </row>
+    <row r="103" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B103">
+        <v>101</v>
+      </c>
+      <c r="C103">
+        <v>913.54</v>
+      </c>
+    </row>
+    <row r="104" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B104">
+        <v>102</v>
+      </c>
+      <c r="C104">
+        <v>902.67</v>
+      </c>
+    </row>
+    <row r="105" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B105">
+        <v>103</v>
+      </c>
+      <c r="C105">
+        <v>894.42</v>
+      </c>
+    </row>
+    <row r="106" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B106">
+        <v>104</v>
+      </c>
+      <c r="C106">
+        <v>886.29</v>
+      </c>
+    </row>
+    <row r="107" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B107">
+        <v>105</v>
+      </c>
+      <c r="C107">
+        <v>876.4</v>
+      </c>
+    </row>
+    <row r="108" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B108">
+        <v>106</v>
+      </c>
+      <c r="C108">
+        <v>867.89</v>
+      </c>
+    </row>
+    <row r="109" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B109">
+        <v>107</v>
+      </c>
+      <c r="C109">
+        <v>859.74</v>
+      </c>
+    </row>
+    <row r="110" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B110">
+        <v>108</v>
+      </c>
+      <c r="C110">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="111" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B111">
+        <v>109</v>
+      </c>
+      <c r="C111">
+        <v>843.72</v>
+      </c>
+    </row>
+    <row r="112" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B112">
+        <v>110</v>
+      </c>
+      <c r="C112">
+        <v>836.18</v>
+      </c>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B113">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B114">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B115">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B116">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B117">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B118">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B119">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B120">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B121">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B122">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B123">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B124">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B125">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B126">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B127">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="128" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B128">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B129">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B130">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B131">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B132">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B133">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B134">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B135">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B136">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="137" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B137">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B138">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B139">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B140">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="141" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B141">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="142" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B142">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B143">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="144" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B144">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B145">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B146">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B147">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B148">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B149">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B150">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B151">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B152">
+        <v>150</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0EDD170-BC0E-4C1C-BC60-B3E743025BB6}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>